--- a/docs/qa/desk-portal-test-cases.xlsx
+++ b/docs/qa/desk-portal-test-cases.xlsx
@@ -730,12 +730,24 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>VPS at the intended commit; api/worker images built after it. main was 4 commits ahead but git diff --name-only showed docs and CI only, no apps/ packages/ tests/ change, so no deploy was owed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -770,12 +782,24 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>api, worker, web up; postgres reports (healthy); keycloak up.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -810,12 +834,24 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>"Database migrated and built-in roles/templates/departments seeded", app started, zero errors since boot.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -850,12 +886,24 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>/version returns a buildId matching the id embedded in the served HTML, so the watchdog has something true to compare. The reload toast itself needs a browser open across a deploy.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -890,12 +938,24 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>200 over TLS, certificate verifies, no redirect to a co-hosted site, http-&gt;https 301.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -930,12 +990,24 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>PKCE S256 + state; desk_pkce/desk_state are Secure, HttpOnly, SameSite=lax, 10 minutes; session cookies set httpOnly/secure/lax; no token material in the HTML and no auth data in browser storage.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -970,12 +1042,24 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Needs a Keycloak user with a temporary password.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1010,12 +1094,24 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Every /dashboard route 307s to login; an authenticated API endpoint returns 401 anonymously.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1050,12 +1146,24 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session held past the 5-minute access-token lifetime.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1090,12 +1198,24 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Clears desk_at, desk_rt and desk_it AND redirects to Keycloak end-session - a real RP-initiated logout, not just local cookie clearing.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1130,12 +1250,24 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Needs a Keycloak user with no portal record.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1170,12 +1302,24 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Needs client-portal credentials.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1210,12 +1354,24 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Production holds ONE tenant, so there is nothing to cross into. Covered by SecurityIsolationTests, which shares one in-memory root between two tenants so an unscoped reader would really leak. Real proof needs a second org.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1250,12 +1406,24 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>As SEC-01.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1290,12 +1458,24 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Invariants hold: zero tenant-scoped rows with a null organization across tickets, notes, companies, mappings and events; zero tickets whose company belongs to another org. The endpoint itself needs a session.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1330,12 +1510,24 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>As SEC-01.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1370,12 +1562,24 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session. The server-side filter is unit-tested in both directions.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1410,12 +1614,24 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1450,12 +1666,24 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session to read the endpoint.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1490,12 +1718,24 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Needs Connectors:BlockPrivateEgress enabled and a connection pointed at a private address.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1530,12 +1770,24 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>A next-page URL on another host is refused by name; covered by A_next_page_url_on_another_host_is_refused.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1570,12 +1822,24 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>The webhook endpoint is not reachable from outside: the API publishes no ports and nginx has no route to it, so a provider cannot deliver one. Owner chose to keep sync on polling, so this stays not-applicable rather than blocked.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1610,12 +1874,24 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session to upload. EICAR handling is unit-tested.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1650,12 +1926,24 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Exactly five 202s then 429. Driven through the honeypot field so nothing was stored - confirmed zero new enquiry rows.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1690,12 +1978,24 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>All seven built-ins present, IsSystemRole, cross-tenant; zero custom roles.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1730,12 +2030,24 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Twenty grants, matching Permissions.ForRole exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1770,12 +2082,24 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Holds connections.view and mappings.view but neither .manage variant, and no users.manage or roles.manage.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1810,12 +2134,24 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>tickets.view.assigned at Assigned(30) scope.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1850,12 +2186,24 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>note.public.add, time.log and update are all at All(0) scope while the ticket view is Assigned - the asymmetry is deliberate; confirm it still matches policy.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1890,12 +2238,24 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Only audit.view, integration.health.view and security.config.view. No write of any kind.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1930,12 +2290,24 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1970,12 +2342,24 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2010,12 +2394,24 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>StaffAssignable restricts assignment to four staff built-ins or a role this org owns, applied at list, picker AND assignment time - the last was the actual hole. 34 RBAC and golden-matrix tests green.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2050,12 +2446,24 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2090,12 +2498,24 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2130,12 +2550,24 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>All eight system templates store only the difference from their base role; three carry zero entries because they ARE their base role.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2170,12 +2602,24 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2210,12 +2654,24 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2250,12 +2706,24 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2290,12 +2758,24 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Enforced case-insensitively on create and on update-excluding-self, and now by the database too: a unique index over (org, lower(email)) was added this run and proven to reject a case-variant duplicate.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2330,12 +2810,24 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2370,12 +2862,24 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2410,12 +2914,24 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>A technician with no email is surfaced as not-in-portal with the reason, never auto-created.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2450,12 +2966,24 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2490,12 +3018,24 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>The one staff user maps to Autotask resource 29682885; no ConnectWise mapping, which is correct because mappings are per connection.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2530,12 +3070,24 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session to log time.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2570,12 +3122,24 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>An unmapped actor resolves to null rather than a guess, in production and in test.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2610,12 +3174,24 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2650,12 +3226,24 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2690,12 +3278,24 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2730,12 +3330,24 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>No board grants exist, so there is nothing to restrict.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2770,12 +3382,24 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2810,12 +3434,24 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Exactly the seven documented defaults, in sort order, all system defaults and active.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2850,12 +3486,24 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Zero duplicates after a dozen-plus API restarts. Non-resurrection holds by construction: an org holding ANY departments is skipped entirely.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2890,12 +3538,24 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2930,12 +3590,24 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>No teams exist.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2970,12 +3642,24 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Every department endpoint carries RequirePermission(UsersManage), reads included.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3010,12 +3694,24 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3930,12 +4626,24 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3970,12 +4678,24 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Zero raw statuses and zero raw priorities on both connections - PsaStatus differs from PortalStatus everywhere a rule exists.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4010,12 +4730,24 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Unmapped values are named in the worker log; zero outstanding after the mappings were completed this run.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4050,12 +4782,24 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>An unmapped value passes through and the ticket still imports.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4090,12 +4834,24 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Zero rows from the inbound ambiguity query, and zero from its outbound mirror.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4130,12 +4886,24 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Needs a portal-side push.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4170,12 +4938,24 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Three provider values are each claimed by two portal values, and in every case exactly one rule is inbound-eligible.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4210,12 +4990,24 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Needs a portal-side status change.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4250,12 +5042,24 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Needs a portal-side status change.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4290,12 +5094,24 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Needs the mapping page.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4330,12 +5146,24 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>Needs the mapping page.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4370,12 +5198,24 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Re-pointing two queue rules moved 124 tickets once the queue joined the update hash - which is how that gap was found.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4410,12 +5250,24 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4450,12 +5302,24 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Every direct edit this run was scoped by PsaConnectionId and its row count checked against what was expected.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4490,12 +5354,24 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session to log time.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4530,12 +5406,24 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>Rules edited in the database took effect on the next tick with no restart.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4570,12 +5458,24 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr"/>
-      <c r="J98" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>Seven Autotask and four ConnectWise companies auto-created, all carrying tickets.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4610,12 +5510,24 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>A full re-sync fetched 135 across two pages plus a next-page call. Before the fix it stopped at 100 and reported success.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4650,12 +5562,24 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>Zero duplicate (connection, external id) pairs.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4690,12 +5614,24 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>Zero page-cap warnings; headroom is 2.7% of the ceiling.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4730,12 +5666,24 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr"/>
-      <c r="J102" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>Quiet cycles report no work and cost about three requests.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4770,12 +5718,24 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>Needs a field-only edit in the PSA the connector actually reads. Two attempts this run never reached the instance in question.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4810,12 +5770,24 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>Needs a portal-side write.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4850,12 +5822,24 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>Autotask 135/135 raise dates, 135 SLA, 113 closures; ConnectWise 13/13 raise and SLA.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4890,12 +5874,24 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>Raise dates span July to September - the PSA date, not the import date.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4930,12 +5926,24 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>ConnectWise sends no closure date because no board status is flagged as closing - confirmed by closedFlag being false on all six tickets sitting in Completed. Absent, not mis-mapped.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4970,12 +5978,24 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>355 notes imported, 216 internal and 139 public.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5010,12 +6030,24 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr"/>
-      <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Time-entry notes import as internal.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5050,12 +6082,24 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr"/>
-      <c r="J110" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Needs a note deleted in the PSA.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5090,12 +6134,24 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Every ticket carries a synced status; none failed.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5130,12 +6186,24 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="5" t="inlineStr"/>
-      <c r="J112" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>Zero sync failures across the run; a failing connection was never induced deliberately on production.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5170,12 +6238,24 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>LastSuccessfulSyncAt advancing is the reliable signal; the summary log line is written only when something changed.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7530,12 +8610,24 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr"/>
-      <c r="I172" s="5" t="inlineStr"/>
-      <c r="J172" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>Events captured from both sources.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -7570,12 +8662,24 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr"/>
-      <c r="I173" s="5" t="inlineStr"/>
-      <c r="J173" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>Events dated 13 Jul to 3 Sep - when they happened, not when they arrived.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -7610,12 +8714,24 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="5" t="inlineStr"/>
-      <c r="J174" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>68 events, 13 daily facts, all 68 aggregated.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7650,12 +8766,24 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr"/>
-      <c r="I175" s="5" t="inlineStr"/>
-      <c r="J175" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>Needs a backdated event; injecting one would corrupt real analytics.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -7690,12 +8818,24 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
-      <c r="I176" s="5" t="inlineStr"/>
-      <c r="J176" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>Three consecutive hourly passes identical - the backfill settled.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -7730,12 +8870,24 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr"/>
-      <c r="I177" s="5" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>As ROLL-04.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7770,12 +8922,24 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
-      <c r="I178" s="5" t="inlineStr"/>
-      <c r="J178" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>As ROLL-04.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7810,12 +8974,24 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr"/>
-      <c r="I179" s="5" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>Nothing is old enough to expire: the oldest event is 54 days against a 396-day horizon. Zero rows past the horizon is no violation, not proof that expiry works. The deletion path is unit-tested only.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9610,12 +10786,24 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
-      <c r="I224" s="5" t="inlineStr"/>
-      <c r="J224" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>A full re-sync of 135 tickets takes about 8 minutes and 279 requests, after two efficiencies landed this run.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9650,12 +10838,24 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H225" s="4" t="inlineStr"/>
-      <c r="I225" s="5" t="inlineStr"/>
-      <c r="J225" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>A quiet cycle costs about three outbound requests.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9690,12 +10890,24 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
-      <c r="I226" s="5" t="inlineStr"/>
-      <c r="J226" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>2.7% and 0.3% of the 5,000-ticket ceiling.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9730,12 +10942,24 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H227" s="4" t="inlineStr"/>
-      <c r="I227" s="5" t="inlineStr"/>
-      <c r="J227" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9770,12 +10994,24 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr"/>
-      <c r="I228" s="5" t="inlineStr"/>
-      <c r="J228" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>Needs several concurrent testers.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -9810,12 +11046,24 @@
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H229" s="4" t="inlineStr"/>
-      <c r="I229" s="5" t="inlineStr"/>
-      <c r="J229" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>Would mean deliberately breaking production.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -9850,12 +11098,24 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H230" s="4" t="inlineStr"/>
-      <c r="I230" s="5" t="inlineStr"/>
-      <c r="J230" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>135 imported with no duplicates.</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -9890,12 +11150,24 @@
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H231" s="4" t="inlineStr"/>
-      <c r="I231" s="5" t="inlineStr"/>
-      <c r="J231" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>Dates and queue all populated; both gaps were found and closed this run.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -9930,12 +11202,24 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H232" s="4" t="inlineStr"/>
-      <c r="I232" s="5" t="inlineStr"/>
-      <c r="J232" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>Zero raw statuses or priorities on either connection.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9970,12 +11254,24 @@
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H233" s="4" t="inlineStr"/>
-      <c r="I233" s="5" t="inlineStr"/>
-      <c r="J233" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>Discovery now offers the value tickets arrive with, held by certification tests on both providers.</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -10010,12 +11306,24 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H234" s="4" t="inlineStr"/>
-      <c r="I234" s="5" t="inlineStr"/>
-      <c r="J234" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>No 405 on the Autotask next page; the fake now refuses a GET as the live API does.</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -10050,12 +11358,24 @@
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H235" s="4" t="inlineStr"/>
-      <c r="I235" s="5" t="inlineStr"/>
-      <c r="J235" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>Needs a portal-side note.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -10090,12 +11410,24 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H236" s="4" t="inlineStr"/>
-      <c r="I236" s="5" t="inlineStr"/>
-      <c r="J236" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>Needs a PSA time entry with internal-only text.</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -10130,12 +11462,24 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H237" s="4" t="inlineStr"/>
-      <c r="I237" s="5" t="inlineStr"/>
-      <c r="J237" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>Needs a picklist value retired in the PSA.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -10170,12 +11514,24 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H238" s="4" t="inlineStr"/>
-      <c r="I238" s="5" t="inlineStr"/>
-      <c r="J238" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I238" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>Facts cover July to September, not just the rolling window.</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -10210,12 +11566,24 @@
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H239" s="4" t="inlineStr"/>
-      <c r="I239" s="5" t="inlineStr"/>
-      <c r="J239" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>540 unit tests green; five defects this run were each hidden at least once by a fake more permissive than the real API, and each fake was tightened.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J239"/>
@@ -10229,10 +11597,13 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Blocked"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
+      <formula>"Partial"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="G2:G239" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Result" prompt="Pick a result" type="list">
-      <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
+      <formula1>"Not run,Pass,Partial,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/qa/desk-portal-test-cases.xlsx
+++ b/docs/qa/desk-portal-test-cases.xlsx
@@ -3746,12 +3746,24 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3786,12 +3798,24 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session. Worth noting for whoever runs it: the one client user has a null ExternalContactId, so he was invited by hand and the contact-import path has never been exercised here.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3826,12 +3850,24 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3866,12 +3902,24 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3906,12 +3954,24 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>All 355 notes carry AuthoredByClient = false - 17 portal-authored, 338 imported. That is the shape of the PR #66 bug, but it is not a regression: both connectors populate the flag and the heal loop rewrites it on every sync, of which many ran. No client has ever written a note in either PSA, so the mechanism is verified and the rendering is not - two different claims.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3946,12 +4006,24 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Zero section grants exist, so there is nothing to delegate.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3986,12 +4058,24 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session. Last-admin protection is unit-tested.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4026,12 +4110,24 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Needs a client session.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4066,12 +4162,24 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>The connection row holds a 32-character opaque id; the material lives in secret_blobs."Ciphertext" as bytea in a separate table. Structural, which is what the case asks - an attempt to measure how printable the ciphertext was returned 257% and meant nothing, because encode(escape) expands bytes.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4106,12 +4214,24 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session. Read-only and safe to run - one call to the PSA.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4146,12 +4266,24 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="5" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Needs credentials typed into a form, which is the tester's to do and not the agent's. Merge-not-clobber is unit-tested.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4186,12 +4318,24 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session. Display only, safe.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4226,12 +4370,24 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session AND stops a live integration syncing. Reversible in seconds, but it is a deliberate outage on production - staging is the honest place for it.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4266,12 +4422,24 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session. Read-only against the PSA, safe.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4306,12 +4474,24 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Map() filters o.IsActive before options reach the mapping UI.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4346,12 +4526,24 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Options carry Value and SyncValue, held by certification tests on both providers.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4386,12 +4578,24 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Rests on the An_import_filter_restricted_to_one_company_excludes_the_others test written this run - production filters are empty, so no live data proves it. The test exists because the fake used to match everything.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4426,12 +4630,24 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>The one to avoid on production: turning the toggle off and re-syncing could reconcile away the 113 already-imported closed Autotask tickets, and recovering them means another full re-sync. Real data movement to prove a toggle.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4466,12 +4682,24 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="5" t="inlineStr"/>
-      <c r="J78" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session. Creates no time entry, so safe to run.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4506,12 +4734,24 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Needs a session, but arguably already covered: the button calls the same ConnectionSyncRunner invoked a dozen times this run by resetting the watermark. Only the HTTP entry point is untested.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4546,12 +4786,24 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Both connections healthy, enabled, synced within the minute, no error.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4586,12 +4838,24 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>A failed run sets Status = Degraded and LastError, cleared on success. Corroborated by the Autotask 405 incident this run, which exercised the path for real - LastError reads empty now precisely because the next success cleared it.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -10466,12 +10730,24 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr"/>
-      <c r="I216" s="5" t="inlineStr"/>
-      <c r="J216" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>All 17 public pages return 200 with real content, not a shell.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -10506,12 +10782,24 @@
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H217" s="4" t="inlineStr"/>
-      <c r="I217" s="5" t="inlineStr"/>
-      <c r="J217" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>Stored with Kind = 0. The test rows were deleted afterwards; the one genuine enquiry on production was left alone.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -10546,12 +10834,24 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
-      <c r="I218" s="5" t="inlineStr"/>
-      <c r="J218" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>Stored with Kind = 1, carrying the preferred time as the visitor worded it.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -10586,12 +10886,24 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H219" s="4" t="inlineStr"/>
-      <c r="I219" s="5" t="inlineStr"/>
-      <c r="J219" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>A filled honeypot answers 202 and stores nothing - confirmed by row count.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -10626,12 +10938,24 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
-      <c r="I220" s="5" t="inlineStr"/>
-      <c r="J220" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>A defect this run, now fixed and verified in production. A 60,000-character message used to return 202 and store exactly 4,000: the sender was thanked and never told, and staff read a message ending mid-sentence with nothing to mark the cut. Every visitor-typed field is now refused when oversized, naming the field and the limit, and nothing is written on a refusal. Live: 60,000 and 4,001 both 400, a normal message 202, no truncated rows. SourcePage is still clipped on purpose - the site fills it in, and a lead should not be lost to the length of our own URL.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -10666,12 +10990,24 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H221" s="4" t="inlineStr"/>
-      <c r="I221" s="5" t="inlineStr"/>
-      <c r="J221" s="4" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Needs an admin session to move an enquiry through its statuses.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -10706,12 +11042,24 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
-      <c r="I222" s="5" t="inlineStr"/>
-      <c r="J222" s="4" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>Twelve unfilled placeholders are live and visible: seven on /privacy (registered address, hosting provider, hosting region, and four retention periods reading "e.g. 24 months" and the like) and five on /terms (two notice periods, the liability cap "e.g. the fees paid in the preceding 12 months", and governing law twice as "your jurisdiction"). A scan for placeholder MARKERS - TBD, TODO, lorem ipsum - finds nothing, because the slots hold ordinary English inside &lt;mark&gt; elements; only grepping "&lt;Fill" in the page sources revealed them. Needs the owner's real values.</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -10746,12 +11094,24 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H223" s="4" t="inlineStr"/>
-      <c r="I223" s="5" t="inlineStr"/>
-      <c r="J223" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Zero cookies are set on any public page, so no banner is owed. The session cookies begin at sign-in and are strictly necessary.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -11581,7 +11941,7 @@
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>540 unit tests green; five defects this run were each hidden at least once by a fake more permissive than the real API, and each fake was tightened.</t>
+          <t>549 unit tests green; five defects this run were each hidden at least once by a fake more permissive than the real API, and each fake was tightened.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/desk-portal-test-cases.xlsx
+++ b/docs/qa/desk-portal-test-cases.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Reference" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$J$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$J$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Needs a client session. The server-side filter is unit-tested in both directions.</t>
+          <t>Exercised on a LOCAL instance running production code, under a real client identity (the dev subject linked to a client company with tickets.view.all removed, so the client branch actually ran - confirmed by the composer offering only "Add a reply"). An internal note was absent from the client payload while the public one was present. Not production, which has no internal notes on a client-visible ticket to test with.</t>
         </is>
       </c>
     </row>
@@ -1948,32 +1948,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>4. Roles and Permissions</t>
+          <t>3. Tenant Isolation and Security</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ROLE-01</t>
+          <t>SEC-13</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Built-in roles exist and are read-only</t>
+          <t>A file posted with an internal note never reaches a client</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/roles as an MSP administrator. Try to edit a built-in role.</t>
+          <t>As staff, post an INTERNAL note on a client's ticket with a file attached (name it obviously, e.g. INTERNAL-credentials.png). Then, as a client user of that company, open the ticket and read the API response, not just the page. Finally take the attachment id from the staff view and call the download endpoint as the client: GET /api/tickets/{ticketId}/attachments/{attachmentId}/download</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>PlatformSuperAdministrator, MspAdministrator, Manager, Technician, ClientAdministrator, ClientUser and Auditor are listed and cannot be edited.</t>
+          <t>The client's detail payload contains neither the internal note NOR its attachment - no file name, size, uploader or id. The download returns 404 (not 403). A file attached to a PUBLIC note, and one attached to no note at all, are both still returned and downloadable - a rule that refuses those has been written too broadly.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Browser. Built-ins are cross-tenant rows - editing one would affect every tenant.</t>
+          <t>DevTools &gt; Network on the ticket detail response, plus curl for the download. CHECK THE PAYLOAD, NOT THE PAGE: the UI hides an internal-note attachment by accident - it matches no rendered message, and the loose-files list takes only attachments with no note - so a leak here looks completely normal on screen. This is how it was missed.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>All seven built-ins present, IsSystemRole, cross-tenant; zero custom roles.</t>
+          <t>A defect this run, found while checking that images render for clients, and now closed. The conversation was filtered for clients and the attachment list beside it was not, so every attachment on a ticket - name, size, uploader and ID - reached the client whatever note it belonged to, and the download endpoint asked only whether it belonged to the ticket. The UI hid them by accident, which is not protection. Both halves were fixed and then exercised on a running instance as a real client identity: an internal note carrying INTERNAL-credentials.png was absent from the payload, its id returned 404 on download, and the public-note and no-note files stayed visible and downloadable at 200. Production held zero attachments on internal notes before and after, so nothing was ever exposed. Held by 4 tests; removing the read filter fails 2 and disabling the endpoint check fails 1.</t>
         </is>
       </c>
     </row>
@@ -2005,27 +2005,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ROLE-02</t>
+          <t>ROLE-01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>MSP administrator permission set</t>
+          <t>Built-in roles exist and are read-only</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/users/{id}/permissions for an MspAdministrator.</t>
+          <t>Open /dashboard/roles as an MSP administrator. Try to edit a built-in role.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Includes org.manage, connections.manage, mappings.manage, users.manage, roles.manage, tickets.view.all, audit.view, enquiries.view and productivity.team.view.</t>
+          <t>PlatformSuperAdministrator, MspAdministrator, Manager, Technician, ClientAdministrator, ClientUser and Auditor are listed and cannot be edited.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>API response against packages/domain/Authorization/Permissions.cs ForRole.</t>
+          <t>Browser. Built-ins are cross-tenant rows - editing one would affect every tenant.</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Twenty grants, matching Permissions.ForRole exactly.</t>
+          <t>All seven built-ins present, IsSystemRole, cross-tenant; zero custom roles.</t>
         </is>
       </c>
     </row>
@@ -2057,27 +2057,27 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ROLE-03</t>
+          <t>ROLE-02</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Manager cannot manage users or connections</t>
+          <t>MSP administrator permission set</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Log in as a Manager. Attempt /dashboard/users and /dashboard/connections edit.</t>
+          <t>GET /api/admin/users/{id}/permissions for an MspAdministrator.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Manager has connections.view and mappings.view but NOT the manage variants, and no users.manage. Read allowed, write refused.</t>
+          <t>Includes org.manage, connections.manage, mappings.manage, users.manage, roles.manage, tickets.view.all, audit.view, enquiries.view and productivity.team.view.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Browser + API 403.</t>
+          <t>API response against packages/domain/Authorization/Permissions.cs ForRole.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Holds connections.view and mappings.view but neither .manage variant, and no users.manage or roles.manage.</t>
+          <t>Twenty grants, matching Permissions.ForRole exactly.</t>
         </is>
       </c>
     </row>
@@ -2109,27 +2109,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ROLE-04</t>
+          <t>ROLE-03</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Technician sees assigned tickets only</t>
+          <t>Manager cannot manage users or connections</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Log in as a Standard Technician and open the ticket list.</t>
+          <t>Log in as a Manager. Attempt /dashboard/users and /dashboard/connections edit.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Only tickets assigned to them (tickets.view.assigned at Assigned scope).</t>
+          <t>Manager has connections.view and mappings.view but NOT the manage variants, and no users.manage. Read allowed, write refused.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL: compare with select count(*) from tickets where "AssignedTechnicianExternalId"='&lt;their external id&gt;'.</t>
+          <t>Browser + API 403.</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>tickets.view.assigned at Assigned(30) scope.</t>
+          <t>Holds connections.view and mappings.view but neither .manage variant, and no users.manage or roles.manage.</t>
         </is>
       </c>
     </row>
@@ -2161,27 +2161,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ROLE-05</t>
+          <t>ROLE-04</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Technician can log time and add public notes on any ticket</t>
+          <t>Technician sees assigned tickets only</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>As a technician, open a ticket they can see and log time / add a note.</t>
+          <t>Log in as a Standard Technician and open the ticket list.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Allowed - tickets.time.log and tickets.note.public.add are granted at All scope by design.</t>
+          <t>Only tickets assigned to them (tickets.view.assigned at Assigned scope).</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Browser. This is deliberate, not a bug: confirm it still matches your policy.</t>
+          <t>Browser + SQL: compare with select count(*) from tickets where "AssignedTechnicianExternalId"='&lt;their external id&gt;'.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>note.public.add, time.log and update are all at All(0) scope while the ticket view is Assigned - the asymmetry is deliberate; confirm it still matches policy.</t>
+          <t>tickets.view.assigned at Assigned(30) scope.</t>
         </is>
       </c>
     </row>
@@ -2213,27 +2213,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ROLE-06</t>
+          <t>ROLE-05</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Auditor is read-only</t>
+          <t>Technician can log time and add public notes on any ticket</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Log in as an Auditor and attempt any write: change a status, save a mapping, edit a user.</t>
+          <t>As a technician, open a ticket they can see and log time / add a note.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>All writes refused; audit and security pages readable.</t>
+          <t>Allowed - tickets.time.log and tickets.note.public.add are granted at All scope by design.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Browser + API.</t>
+          <t>Browser. This is deliberate, not a bug: confirm it still matches your policy.</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Only audit.view, integration.health.view and security.config.view. No write of any kind.</t>
+          <t>note.public.add, time.log and update are all at All(0) scope while the ticket view is Assigned - the asymmetry is deliberate; confirm it still matches policy.</t>
         </is>
       </c>
     </row>
@@ -2265,32 +2265,32 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ROLE-07</t>
+          <t>ROLE-06</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Custom role creation</t>
+          <t>Auditor is read-only</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Create a tenant role 'Dispatcher QA' from the catalogue, grant tickets.view.all and tickets.update only, assign it to a test user.</t>
+          <t>Log in as an Auditor and attempt any write: change a status, save a mapping, edit a user.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>The user gains exactly those two capabilities and nothing else.</t>
+          <t>All writes refused; audit and security pages readable.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/dashboard/roles then verify with /dashboard/permissions.</t>
+          <t>Browser + API.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>Only audit.view, integration.health.view and security.config.view. No write of any kind.</t>
         </is>
       </c>
     </row>
@@ -2317,27 +2317,27 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ROLE-08</t>
+          <t>ROLE-07</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Duplicate-from-built-in</t>
+          <t>Custom role creation</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Use Duplicate on a built-in role, then edit the copy.</t>
+          <t>Create a tenant role 'Dispatcher QA' from the catalogue, grant tickets.view.all and tickets.update only, assign it to a test user.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>The copy is tenant-owned and editable; the built-in is unchanged.</t>
+          <t>The user gains exactly those two capabilities and nothing else.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL: the new row has a non-null MspOrganizationId.</t>
+          <t>/dashboard/roles then verify with /dashboard/permissions.</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2369,32 +2369,32 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ROLE-09</t>
+          <t>ROLE-08</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Privilege escalation is blocked</t>
+          <t>Duplicate-from-built-in</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>As an MSP administrator, attempt to assign PlatformSuperAdministrator to another user, including by POSTing the role id directly to /api/admin/users/{id}/roles/{roleId}.</t>
+          <t>Use Duplicate on a built-in role, then edit the copy.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Refused. Only the 4 staff built-ins plus tenant customs are assignable.</t>
+          <t>The copy is tenant-owned and editable; the built-in is unchanged.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>API. This is a real escalation hole that was closed - it must stay closed.</t>
+          <t>Browser + SQL: the new row has a non-null MspOrganizationId.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>StaffAssignable restricts assignment to four staff built-ins or a role this org owns, applied at list, picker AND assignment time - the last was the actual hole. 34 RBAC and golden-matrix tests green.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -2421,32 +2421,32 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ROLE-10</t>
+          <t>ROLE-09</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Cannot edit a role you currently hold</t>
+          <t>Privilege escalation is blocked</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>As a user holding custom role R, try to edit R.</t>
+          <t>As an MSP administrator, attempt to assign PlatformSuperAdministrator to another user, including by POSTing the role id directly to /api/admin/users/{id}/roles/{roleId}.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Forbidden.</t>
+          <t>Refused. Only the 4 staff built-ins plus tenant customs are assignable.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Browser + API 403.</t>
+          <t>API. This is a real escalation hole that was closed - it must stay closed.</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>StaffAssignable restricts assignment to four staff built-ins or a role this org owns, applied at list, picker AND assignment time - the last was the actual hole. 34 RBAC and golden-matrix tests green.</t>
         </is>
       </c>
     </row>
@@ -2473,27 +2473,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ROLE-11</t>
+          <t>ROLE-10</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cannot delete a role still assigned</t>
+          <t>Cannot edit a role you currently hold</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Delete a custom role that a user holds.</t>
+          <t>As a user holding custom role R, try to edit R.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Refused with a clear message naming the holders.</t>
+          <t>Forbidden.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + API 403.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2525,32 +2525,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ROLE-12</t>
+          <t>ROLE-11</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Permission templates apply as a diff</t>
+          <t>Cannot delete a role still assigned</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Apply the 'Senior Technician' template to a user via POST /api/admin/users/{id}/apply-template/{templateId}.</t>
+          <t>Delete a custom role that a user holds.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>The base role is assigned AND the template's override entries are materialised on top. Templates hold only the difference from their base role.</t>
+          <t>Refused with a clear message naming the holders.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/users/{id}/permissions before and after.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>All eight system templates store only the difference from their base role; three carry zero entries because they ARE their base role.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ROLE-13</t>
+          <t>ROLE-12</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Effective permission explorer is accurate</t>
+          <t>Permission templates apply as a diff</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/permissions, pick tickets.view.all, and compare the holder list with a manual check of three users.</t>
+          <t>Apply the 'Senior Technician' template to a user via POST /api/admin/users/{id}/apply-template/{templateId}.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Holders match, and each row names the roles that contributed the grant. An override-deny shows as 'Override - denied (role grant from: X)'.</t>
+          <t>The base role is assigned AND the template's override entries are materialised on top. Templates hold only the difference from their base role.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Browser. This page is engine-resolved, so it is also a test of the engine itself.</t>
+          <t>GET /api/admin/users/{id}/permissions before and after.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>All eight system templates store only the difference from their base role; three carry zero entries because they ARE their base role.</t>
         </is>
       </c>
     </row>
@@ -2629,27 +2629,27 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>ROLE-14</t>
+          <t>ROLE-13</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Override deny beats a role grant</t>
+          <t>Effective permission explorer is accurate</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Give a user a role granting tickets.update, then add an explicit deny override.</t>
+          <t>Open /dashboard/permissions, pick tickets.view.all, and compare the holder list with a manual check of three users.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>The user cannot update tickets, and the explorer explains why.</t>
+          <t>Holders match, and each row names the roles that contributed the grant. An override-deny shows as 'Override - denied (role grant from: X)'.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Browser + API 403 on a status change.</t>
+          <t>Browser. This page is engine-resolved, so it is also a test of the engine itself.</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2676,32 +2676,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>5. Staff Users and Technician Registration</t>
+          <t>4. Roles and Permissions</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>USER-01</t>
+          <t>ROLE-14</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Create a staff user</t>
+          <t>Override deny beats a role grant</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>/dashboard/users &gt; Add user. Supply name, email, role.</t>
+          <t>Give a user a role granting tickets.update, then add an explicit deny override.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>User is created, appears in the list, and can be opened at /dashboard/users/{id}.</t>
+          <t>The user cannot update tickets, and the explorer explains why.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL: select * from app_users order by "CreatedAt" desc limit 1.</t>
+          <t>Browser + API 403 on a status change.</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>USER-02</t>
+          <t>USER-01</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Email is required and unique</t>
+          <t>Create a staff user</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Attempt to create a second user with an existing email, and one with no email.</t>
+          <t>/dashboard/users &gt; Add user. Supply name, email, role.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Both refused with a clear message.</t>
+          <t>User is created, appears in the list, and can be opened at /dashboard/users/{id}.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + SQL: select * from app_users order by "CreatedAt" desc limit 1.</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Enforced case-insensitively on create and on update-excluding-self, and now by the database too: a unique index over (org, lower(email)) was added this run and proven to reject a case-variant duplicate.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>USER-03</t>
+          <t>USER-02</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Bulk user creation</t>
+          <t>Email is required and unique</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/users/bulk with three users, one of them invalid.</t>
+          <t>Attempt to create a second user with an existing email, and one with no email.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Valid rows are created, the invalid one is reported. No partial-silent failure.</t>
+          <t>Both refused with a clear message.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>API response + SQL count.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>Enforced case-insensitively on create and on update-excluding-self, and now by the database too: a unique index over (org, lower(email)) was added this run and proven to reject a case-variant duplicate.</t>
         </is>
       </c>
     </row>
@@ -2837,27 +2837,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>USER-04</t>
+          <t>USER-03</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Import technicians from the PSA</t>
+          <t>Bulk user creation</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/dashboard/users &gt; Import from PSA. Select the Autotask connection.</t>
+          <t>POST /api/admin/users/bulk with three users, one of them invalid.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Active PSA technicians are listed with their names and emails.</t>
+          <t>Valid rows are created, the invalid one is reported. No partial-silent failure.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/psa-technicians/{psaConnectionId}.</t>
+          <t>API response + SQL count.</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2889,32 +2889,32 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>USER-05</t>
+          <t>USER-04</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>A PSA technician with no email is refused</t>
+          <t>Import technicians from the PSA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Attempt to import a technician whose PSA record has no email address.</t>
+          <t>/dashboard/users &gt; Import from PSA. Select the Autotask connection.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Refused with a reason, not silently skipped and not created with a placeholder.</t>
+          <t>Active PSA technicians are listed with their names and emails.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>API response. Provisioning deliberately will not invent an identity.</t>
+          <t>GET /api/admin/psa-technicians/{psaConnectionId}.</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>A technician with no email is surfaced as not-in-portal with the reason, never auto-created.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -2941,32 +2941,32 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>USER-06</t>
+          <t>USER-05</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Importing a technician creates a usable portal user</t>
+          <t>A PSA technician with no email is refused</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/psa-technicians/{connectionId}/{externalTechnicianId}.</t>
+          <t>Attempt to import a technician whose PSA record has no email address.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>A portal user is created AND bound to that PSA technician id.</t>
+          <t>Refused with a reason, not silently skipped and not created with a placeholder.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/users/{id}/psa-identities.</t>
+          <t>API response. Provisioning deliberately will not invent an identity.</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>A technician with no email is surfaced as not-in-portal with the reason, never auto-created.</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>USER-07</t>
+          <t>USER-06</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Per-connection PSA identity mapping</t>
+          <t>Importing a technician creates a usable portal user</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/admin/users/{id}/psa-identities/{psaConnectionId} to map a user to an Autotask resource id, then map the same user on the ConnectWise connection to a member id.</t>
+          <t>POST /api/admin/psa-technicians/{connectionId}/{externalTechnicianId}.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Both mappings coexist. They are per connection because an Autotask numeric resourceID and a ConnectWise member identifier are different kinds of thing.</t>
+          <t>A portal user is created AND bound to that PSA technician id.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>SQL: select * from user_psa_identities where "AppUserId"='&lt;id&gt;'.</t>
+          <t>GET /api/admin/users/{id}/psa-identities.</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>The one staff user maps to Autotask resource 29682885; no ConnectWise mapping, which is correct because mappings are per connection.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -3045,32 +3045,32 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>USER-08</t>
+          <t>USER-07</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Time is attributed to the mapped technician</t>
+          <t>Per-connection PSA identity mapping</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>As a mapped user, log time on a ticket, then check the entry in the PSA.</t>
+          <t>PUT /api/admin/users/{id}/psa-identities/{psaConnectionId} to map a user to an Autotask resource id, then map the same user on the ConnectWise connection to a member id.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>The PSA time entry is owned by that technician, not by the API integration user.</t>
+          <t>Both mappings coexist. They are per connection because an Autotask numeric resourceID and a ConnectWise member identifier are different kinds of thing.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + portal time entry list.</t>
+          <t>SQL: select * from user_psa_identities where "AppUserId"='&lt;id&gt;'.</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Needs a session to log time.</t>
+          <t>The one staff user maps to Autotask resource 29682885; no ConnectWise mapping, which is correct because mappings are per connection.</t>
         </is>
       </c>
     </row>
@@ -3097,32 +3097,32 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>USER-09</t>
+          <t>USER-08</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>An unmapped user is not guessed at</t>
+          <t>Time is attributed to the mapped technician</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Log activity as a portal user with no PSA identity, then run the rollup.</t>
+          <t>As a mapped user, log time on a ticket, then check the entry in the PSA.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>The daily fact carries a null actor rather than an attributed guess.</t>
+          <t>The PSA time entry is owned by that technician, not by the API integration user.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "ActorExternalId" from activity_daily_facts order by "Day" desc limit 5.</t>
+          <t>PSA UI + portal time entry list.</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>An unmapped actor resolves to null rather than a guess, in production and in test.</t>
+          <t>Needs a session to log time.</t>
         </is>
       </c>
     </row>
@@ -3149,32 +3149,32 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>USER-10</t>
+          <t>USER-09</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Deactivate a user</t>
+          <t>An unmapped user is not guessed at</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/admin/users/{id}/active with false, then try to log in as them.</t>
+          <t>Log activity as a portal user with no PSA identity, then run the rollup.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Login is refused or lands with no access; the user remains in the list as inactive for audit history.</t>
+          <t>The daily fact carries a null actor rather than an attributed guess.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>SQL: select "ActorExternalId" from activity_daily_facts order by "Day" desc limit 5.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>An unmapped actor resolves to null rather than a guess, in production and in test.</t>
         </is>
       </c>
     </row>
@@ -3201,27 +3201,27 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>USER-11</t>
+          <t>USER-10</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Delete a user</t>
+          <t>Deactivate a user</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/admin/users/{id} for a user with no history, and one with ticket history.</t>
+          <t>PUT /api/admin/users/{id}/active with false, then try to log in as them.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Behaviour is consistent and explained; historical attribution is not silently orphaned.</t>
+          <t>Login is refused or lands with no access; the user remains in the list as inactive for audit history.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>API + SQL.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -3253,27 +3253,27 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>USER-12</t>
+          <t>USER-11</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Profile photo upload and removal</t>
+          <t>Delete a user</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>POST then DELETE /api/admin/users/{id}/photo.</t>
+          <t>DELETE /api/admin/users/{id} for a user with no history, and one with ticket history.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Photo appears in the user list and detail, and removal restores the initials avatar.</t>
+          <t>Behaviour is consistent and explained; historical attribution is not silently orphaned.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>API + SQL.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>USER-13</t>
+          <t>USER-12</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Board / queue access grants</t>
+          <t>Profile photo upload and removal</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/admin/users/{id}/board-grants restricting a technician to one board.</t>
+          <t>POST then DELETE /api/admin/users/{id}/photo.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>The technician sees only tickets on that board.</t>
+          <t>Photo appears in the user list and detail, and removal restores the initials avatar.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Browser as that user + SQL cross-check.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>No board grants exist, so there is nothing to restrict.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -3357,32 +3357,32 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>USER-14</t>
+          <t>USER-13</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>User detail tabs load</t>
+          <t>Board / queue access grants</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/users/{id} and visit every tab.</t>
+          <t>PUT /api/admin/users/{id}/board-grants restricting a technician to one board.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>All tabs render with real data and no console errors.</t>
+          <t>The technician sees only tickets on that board.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Browser DevTools console.</t>
+          <t>Browser as that user + SQL cross-check.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3397,44 +3397,44 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>No board grants exist, so there is nothing to restrict.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>6. Departments and Teams</t>
+          <t>5. Staff Users and Technician Registration</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ORG-01</t>
+          <t>USER-14</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Default departments are seeded</t>
+          <t>User detail tabs load</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Create a new organization and inspect its departments.</t>
+          <t>Open /dashboard/users/{id} and visit every tab.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>IT Support, NOC, Projects, Sales, Billing, Administration, Security.</t>
+          <t>All tabs render with real data and no console errors.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "Name" from departments where "MspOrganizationId"='&lt;new org&gt;'.</t>
+          <t>Browser DevTools console.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Exactly the seven documented defaults, in sort order, all system defaults and active.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -3461,27 +3461,27 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>ORG-02</t>
+          <t>ORG-01</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Seeding is idempotent and non-resurrecting</t>
+          <t>Default departments are seeded</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Delete one default department, then restart the API.</t>
+          <t>Create a new organization and inspect its departments.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The deleted department stays deleted. Seeding skips any org that already has ANY departments.</t>
+          <t>IT Support, NOC, Projects, Sales, Billing, Administration, Security.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>SQL before and after restart.</t>
+          <t>SQL: select "Name" from departments where "MspOrganizationId"='&lt;new org&gt;'.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Zero duplicates after a dozen-plus API restarts. Non-resurrection holds by construction: an org holding ANY departments is skipped entirely.</t>
+          <t>Exactly the seven documented defaults, in sort order, all system defaults and active.</t>
         </is>
       </c>
     </row>
@@ -3513,32 +3513,32 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ORG-03</t>
+          <t>ORG-02</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Create, rename, deactivate a department</t>
+          <t>Seeding is idempotent and non-resurrecting</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/departments, PUT it, then PUT .../active false.</t>
+          <t>Delete one default department, then restart the API.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Each step succeeds and is reflected in /dashboard/departments.</t>
+          <t>The deleted department stays deleted. Seeding skips any org that already has ANY departments.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Browser + API.</t>
+          <t>SQL before and after restart.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>Zero duplicates after a dozen-plus API restarts. Non-resurrection holds by construction: an org holding ANY departments is skipped entirely.</t>
         </is>
       </c>
     </row>
@@ -3565,32 +3565,32 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ORG-04</t>
+          <t>ORG-03</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Team membership</t>
+          <t>Create, rename, deactivate a department</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Create a team, add and remove a user via POST/DELETE /api/admin/users/{id}/teams/{teamId}.</t>
+          <t>POST /api/admin/departments, PUT it, then PUT .../active false.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Membership updates immediately and appears on the user detail page.</t>
+          <t>Each step succeeds and is reflected in /dashboard/departments.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + API.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>No teams exist.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -3617,32 +3617,32 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>ORG-05</t>
+          <t>ORG-04</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Departments page is permission gated</t>
+          <t>Team membership</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/departments as a Technician.</t>
+          <t>Create a team, add and remove a user via POST/DELETE /api/admin/users/{id}/teams/{teamId}.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Refused - the page is gated on users.manage by design (no dedicated permission).</t>
+          <t>Membership updates immediately and appears on the user detail page.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Browser + API 403.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Every department endpoint carries RequirePermission(UsersManage), reads included.</t>
+          <t>No teams exist.</t>
         </is>
       </c>
     </row>
@@ -3669,32 +3669,32 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ORG-06</t>
+          <t>ORG-05</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Org structure endpoint</t>
+          <t>Departments page is permission gated</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/org-structure.</t>
+          <t>Open /dashboard/departments as a Technician.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Returns the department/team tree with member counts matching the database.</t>
+          <t>Refused - the page is gated on users.manage by design (no dedicated permission).</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>API + SQL counts.</t>
+          <t>Browser + API 403.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3709,39 +3709,39 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>Every department endpoint carries RequirePermission(UsersManage), reads included.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>7. Client Users and the Client Portal</t>
+          <t>6. Departments and Teams</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-01</t>
+          <t>ORG-06</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Invite a client user</t>
+          <t>Org structure endpoint</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>/control-panel/users &gt; invite, or POST /api/control-panel/users.</t>
+          <t>GET /api/admin/org-structure.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Invited user appears with the correct company and no staff permissions.</t>
+          <t>Returns the department/team tree with member counts matching the database.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL: select * from client_users order by "CreatedAt" desc limit 1.</t>
+          <t>API + SQL counts.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Needs a client session.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -3773,27 +3773,27 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-02</t>
+          <t>CLIENT-01</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Import contacts from the PSA</t>
+          <t>Invite a client user</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Control Panel &gt; Accounts &gt; Import from PSA (POST /api/control-panel/import-from-psa).</t>
+          <t>/control-panel/users &gt; invite, or POST /api/control-panel/users.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PSA contacts become client_users with their real email addresses.</t>
+          <t>Invited user appears with the correct company and no staff permissions.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL count before/after.</t>
+          <t>Browser + SQL: select * from client_users order by "CreatedAt" desc limit 1.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session. Worth noting for whoever runs it: the one client user has a null ExternalContactId, so he was invited by hand and the contact-import path has never been exercised here.</t>
+          <t>Needs a client session.</t>
         </is>
       </c>
     </row>
@@ -3825,27 +3825,27 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-03</t>
+          <t>CLIENT-02</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Client can raise a ticket</t>
+          <t>Import contacts from the PSA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>As a client user, create a ticket from the portal.</t>
+          <t>Control Panel &gt; Accounts &gt; Import from PSA (POST /api/control-panel/import-from-psa).</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Ticket is created in the PSA first, then stored locally with a portal-origin sync event.</t>
+          <t>PSA contacts become client_users with their real email addresses.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Portal + PSA UI. Confirm the ticket exists in the PSA, not only in the portal.</t>
+          <t>Browser + SQL count before/after.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Needs a client session.</t>
+          <t>Needs an admin session. Worth noting for whoever runs it: the one client user has a null ExternalContactId, so he was invited by hand and the contact-import path has never been exercised here.</t>
         </is>
       </c>
     </row>
@@ -3877,27 +3877,27 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-04</t>
+          <t>CLIENT-03</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Client can reply but not use staff tooling</t>
+          <t>Client can raise a ticket</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket as a client user.</t>
+          <t>As a client user, create a ticket from the portal.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Reply box present. No time panel, no assignment control, no internal-note toggle; the status is a static badge.</t>
+          <t>Ticket is created in the PSA first, then stored locally with a portal-origin sync event.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Portal + PSA UI. Confirm the ticket exists in the PSA, not only in the portal.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3929,32 +3929,32 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-05</t>
+          <t>CLIENT-04</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Client thread sides and attribution</t>
+          <t>Client can reply but not use staff tooling</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>View a thread containing both client and staff notes.</t>
+          <t>Open a ticket as a client user.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Client messages left, staff right, with correct author names.</t>
+          <t>Reply box present. No time panel, no assignment control, no internal-note toggle; the status is a static badge.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Browser. Notes imported before FromClient was captured keep their old side until re-imported - do not report that as a new bug.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>All 355 notes carry AuthoredByClient = false - 17 portal-authored, 338 imported. That is the shape of the PR #66 bug, but it is not a regression: both connectors populate the flag and the heal loop rewrites it on every sync, of which many ran. No client has ever written a note in either PSA, so the mechanism is verified and the rendering is not - two different claims.</t>
+          <t>Needs a client session.</t>
         </is>
       </c>
     </row>
@@ -3981,32 +3981,32 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-06</t>
+          <t>CLIENT-05</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Section delegation</t>
+          <t>Client thread sides and attribution</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Grant a non-admin client user access to only the Instructions section for one account.</t>
+          <t>View a thread containing both client and staff notes.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>That user sees Instructions for that account and nothing else.</t>
+          <t>Client messages left, staff right, with correct author names.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Browser as that user.</t>
+          <t>Browser. Notes imported before FromClient was captured keep their old side until re-imported - do not report that as a new bug.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Zero section grants exist, so there is nothing to delegate.</t>
+          <t>All 355 notes carry AuthoredByClient = false - 17 portal-authored, 338 imported. That is the shape of the PR #66 bug, but it is not a regression: both connectors populate the flag and the heal loop rewrites it on every sync, of which many ran. No client has ever written a note in either PSA, so the mechanism is verified and the rendering is not - two different claims.</t>
         </is>
       </c>
     </row>
@@ -4033,32 +4033,32 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-07</t>
+          <t>CLIENT-06</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Last client admin cannot be removed</t>
+          <t>Section delegation</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Attempt to deactivate the only client administrator for a company.</t>
+          <t>Grant a non-admin client user access to only the Instructions section for one account.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Refused.</t>
+          <t>That user sees Instructions for that account and nothing else.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser as that user.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Needs a client session. Last-admin protection is unit-tested.</t>
+          <t>Zero section grants exist, so there is nothing to delegate.</t>
         </is>
       </c>
     </row>
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>CLIENT-08</t>
+          <t>CLIENT-07</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Client cannot see another company</t>
+          <t>Last client admin cannot be removed</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>As a client user of company X, request a ticket belonging to company Y.</t>
+          <t>Attempt to deactivate the only client administrator for a company.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>API.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -4125,44 +4125,44 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Needs a client session.</t>
+          <t>Needs a client session. Last-admin protection is unit-tested.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>8. PSA Connections</t>
+          <t>7. Client Users and the Client Portal</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>CONN-01</t>
+          <t>CLIENT-08</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Create a connection</t>
+          <t>Client cannot see another company</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>/dashboard/connections &gt; Add. Enter endpoint and credentials. NOTE: the tester enters credentials themselves - never paste them into a chat or a ticket.</t>
+          <t>As a client user of company X, request a ticket belonging to company Y.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Connection saved; credentials go to the encrypted secret store and only a reference is on the row.</t>
+          <t>Refused.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "CredentialSecretRef" from psa_connections - it is a reference, not a secret.</t>
+          <t>API.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>The connection row holds a 32-character opaque id; the material lives in secret_blobs."Ciphertext" as bytea in a separate table. Structural, which is what the case asks - an attempt to measure how printable the ciphertext was returned 257% and meant nothing, because encode(escape) expands bytes.</t>
+          <t>Needs a client session.</t>
         </is>
       </c>
     </row>
@@ -4189,32 +4189,32 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>CONN-02</t>
+          <t>CONN-01</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Test connection</t>
+          <t>Create a connection</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/connections/{id}/test.</t>
+          <t>/dashboard/connections &gt; Add. Enter endpoint and credentials. NOTE: the tester enters credentials themselves - never paste them into a chat or a ticket.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Status becomes Healthy on success; a wrong credential yields the provider's own error message, not a generic 500.</t>
+          <t>Connection saved; credentials go to the encrypted secret store and only a reference is on the row.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Browser + API. Deliberately break a credential to see the real message.</t>
+          <t>SQL: select "CredentialSecretRef" from psa_connections - it is a reference, not a secret.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Needs a session. Read-only and safe to run - one call to the PSA.</t>
+          <t>The connection row holds a 32-character opaque id; the material lives in secret_blobs."Ciphertext" as bytea in a separate table. Structural, which is what the case asks - an attempt to measure how printable the ciphertext was returned 257% and meant nothing, because encode(escape) expands bytes.</t>
         </is>
       </c>
     </row>
@@ -4241,27 +4241,27 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>CONN-03</t>
+          <t>CONN-02</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Credential rotation merges rather than clobbers</t>
+          <t>Test connection</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Edit a connection and change ONLY one credential field, leaving the others blank.</t>
+          <t>POST /api/admin/connections/{id}/test.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Typed values are merged over stored ones; untouched fields are preserved.</t>
+          <t>Status becomes Healthy on success; a wrong credential yields the provider's own error message, not a generic 500.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Re-run Test connection - it must still succeed.</t>
+          <t>Browser + API. Deliberately break a credential to see the real message.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Needs credentials typed into a form, which is the tester's to do and not the agent's. Merge-not-clobber is unit-tested.</t>
+          <t>Needs a session. Read-only and safe to run - one call to the PSA.</t>
         </is>
       </c>
     </row>
@@ -4293,27 +4293,27 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>CONN-04</t>
+          <t>CONN-03</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Per-field stored-credential chips</t>
+          <t>Credential rotation merges rather than clobbers</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Open the edit form for a configured connection.</t>
+          <t>Edit a connection and change ONLY one credential field, leaving the others blank.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Each credential field shows Stored or Nothing stored. No secret value is displayed.</t>
+          <t>Typed values are merged over stored ones; untouched fields are preserved.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Re-run Test connection - it must still succeed.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Needs a session. Display only, safe.</t>
+          <t>Needs credentials typed into a form, which is the tester's to do and not the agent's. Merge-not-clobber is unit-tested.</t>
         </is>
       </c>
     </row>
@@ -4345,27 +4345,27 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CONN-05</t>
+          <t>CONN-04</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Enable / disable</t>
+          <t>Per-field stored-credential chips</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/connections/{id}/enabled false.</t>
+          <t>Open the edit form for a configured connection.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sync stops for that connection; the UI shows it disabled; no errors are logged.</t>
+          <t>Each credential field shows Stored or Nothing stored. No secret value is displayed.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Worker log - no further PSA calls for that connection.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Needs a session AND stops a live integration syncing. Reversible in seconds, but it is a deliberate outage on production - staging is the honest place for it.</t>
+          <t>Needs a session. Display only, safe.</t>
         </is>
       </c>
     </row>
@@ -4397,27 +4397,27 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>CONN-06</t>
+          <t>CONN-05</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Field discovery</t>
+          <t>Enable / disable</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/connections/{id}/fields/refresh then GET .../fields.</t>
+          <t>POST /api/admin/connections/{id}/enabled false.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Boards/queues, statuses, priorities, categories, work types, work roles and technicians come back populated.</t>
+          <t>Sync stops for that connection; the UI shows it disabled; no errors are logged.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>API. Compare option counts against the PSA UI.</t>
+          <t>Worker log - no further PSA calls for that connection.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Needs a session. Read-only against the PSA, safe.</t>
+          <t>Needs a session AND stops a live integration syncing. Reversible in seconds, but it is a deliberate outage on production - staging is the honest place for it.</t>
         </is>
       </c>
     </row>
@@ -4449,32 +4449,32 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>CONN-07</t>
+          <t>CONN-06</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Retired picklist values are excluded</t>
+          <t>Field discovery</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Retire a status in the PSA, refresh fields, and open the mapping page.</t>
+          <t>POST /api/admin/connections/{id}/fields/refresh then GET .../fields.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>The retired value no longer appears as a selectable option, and any rule still pointing at it shows red 'Not accepted by PSA' rather than green Mapped.</t>
+          <t>Boards/queues, statuses, priorities, categories, work types, work roles and technicians come back populated.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Browser. This is a real defect class - retired values saved fine and were rejected on every write.</t>
+          <t>API. Compare option counts against the PSA UI.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Map() filters o.IsActive before options reach the mapping UI.</t>
+          <t>Needs a session. Read-only against the PSA, safe.</t>
         </is>
       </c>
     </row>
@@ -4501,27 +4501,27 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>CONN-08</t>
+          <t>CONN-07</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Discovery offers two representations</t>
+          <t>Retired picklist values are excluded</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Inspect GET /api/admin/connections/{id}/fields for queuesOrBoards.</t>
+          <t>Retire a status in the PSA, refresh fields, and open the mapping page.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Each option carries value (the id, sent TO the provider) and syncValue (the name, what tickets ARRIVE with). For queues these differ.</t>
+          <t>The retired value no longer appears as a selectable option, and any rule still pointing at it shows red 'Not accepted by PSA' rather than green Mapped.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Raw JSON. This split is what makes mapping and filtering both work.</t>
+          <t>Browser. This is a real defect class - retired values saved fine and were rejected on every write.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Options carry Value and SyncValue, held by certification tests on both providers.</t>
+          <t>Map() filters o.IsActive before options reach the mapping UI.</t>
         </is>
       </c>
     </row>
@@ -4553,27 +4553,27 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>CONN-09</t>
+          <t>CONN-08</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Import filters</t>
+          <t>Discovery offers two representations</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Set FilterQueueIds / FilterCompanyIds / FilterActiveWithinDays and run a sync.</t>
+          <t>Inspect GET /api/admin/connections/{id}/fields for queuesOrBoards.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Only matching tickets are imported. Filters are applied provider-side AND re-applied client-side so both connectors behave identically.</t>
+          <t>Each option carries value (the id, sent TO the provider) and syncValue (the name, what tickets ARRIVE with). For queues these differ.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>SQL ticket count + worker log.</t>
+          <t>Raw JSON. This split is what makes mapping and filtering both work.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Rests on the An_import_filter_restricted_to_one_company_excludes_the_others test written this run - production filters are empty, so no live data proves it. The test exists because the fake used to match everything.</t>
+          <t>Options carry Value and SyncValue, held by certification tests on both providers.</t>
         </is>
       </c>
     </row>
@@ -4605,32 +4605,32 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>CONN-10</t>
+          <t>CONN-09</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Include closed tickets toggle</t>
+          <t>Import filters</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Turn ImportClosedTickets off, force a full re-sync, then on again.</t>
+          <t>Set FilterQueueIds / FilterCompanyIds / FilterActiveWithinDays and run a sync.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Closed tickets are excluded then included. Closed rows already imported keep their data.</t>
+          <t>Only matching tickets are imported. Filters are applied provider-side AND re-applied client-side so both connectors behave identically.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>SQL: count(*) filter (where "ClosedAt" is not null).</t>
+          <t>SQL ticket count + worker log.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>The one to avoid on production: turning the toggle off and re-syncing could reconcile away the 113 already-imported closed Autotask tickets, and recovering them means another full re-sync. Real data movement to prove a toggle.</t>
+          <t>Rests on the An_import_filter_restricted_to_one_company_excludes_the_others test written this run - production filters are empty, so no live data proves it. The test exists because the fake used to match everything.</t>
         </is>
       </c>
     </row>
@@ -4657,27 +4657,27 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>CONN-11</t>
+          <t>CONN-10</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Time entry readiness check</t>
+          <t>Include closed tickets toggle</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/connections/{id}/check-time-entry.</t>
+          <t>Turn ImportClosedTickets off, force a full re-sync, then on again.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Autotask reports by name: no technician set / technician gone / holds no active role / configured role not held (listing the roles they DO hold) / Ready. No time entry is created.</t>
+          <t>Closed tickets are excluded then included. Closed rows already imported keep their data.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>API + SQL: confirm no new time entry row exists.</t>
+          <t>SQL: count(*) filter (where "ClosedAt" is not null).</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Needs a session. Creates no time entry, so safe to run.</t>
+          <t>The one to avoid on production: turning the toggle off and re-syncing could reconcile away the 113 already-imported closed Autotask tickets, and recovering them means another full re-sync. Real data movement to prove a toggle.</t>
         </is>
       </c>
     </row>
@@ -4709,27 +4709,27 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>CONN-12</t>
+          <t>CONN-11</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Sync now</t>
+          <t>Time entry readiness check</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/connections/{id}/sync.</t>
+          <t>POST /api/admin/connections/{id}/check-time-entry.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>A sync runs immediately and the result is reported.</t>
+          <t>Autotask reports by name: no technician set / technician gone / holds no active role / configured role not held (listing the roles they DO hold) / Ready. No time entry is created.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Worker/API log.</t>
+          <t>API + SQL: confirm no new time entry row exists.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Needs a session, but arguably already covered: the button calls the same ConnectionSyncRunner invoked a dozen times this run by resetting the watermark. Only the HTTP entry point is untested.</t>
+          <t>Needs a session. Creates no time entry, so safe to run.</t>
         </is>
       </c>
     </row>
@@ -4761,32 +4761,32 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>CONN-13</t>
+          <t>CONN-12</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Connection health page</t>
+          <t>Sync now</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/health.</t>
+          <t>POST /api/admin/connections/{id}/sync.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Shows last successful sync, last health check and last error per connection, matching SQL.</t>
+          <t>A sync runs immediately and the result is reported.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL on psa_connections.</t>
+          <t>Worker/API log.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Both connections healthy, enabled, synced within the minute, no error.</t>
+          <t>Needs a session, but arguably already covered: the button calls the same ConnectionSyncRunner invoked a dozen times this run by resetting the watermark. Only the HTTP entry point is untested.</t>
         </is>
       </c>
     </row>
@@ -4813,27 +4813,27 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>CONN-14</t>
+          <t>CONN-13</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Failure marks the connection degraded</t>
+          <t>Connection health page</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Temporarily point a connection at an unreachable endpoint and let a sync run.</t>
+          <t>Open /dashboard/health.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Status becomes Failed/Degraded with the real reason in LastError, and the loop keeps running for the other connection.</t>
+          <t>Shows last successful sync, last health check and last error per connection, matching SQL.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>SQL + worker log.</t>
+          <t>Browser + SQL on psa_connections.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4853,44 +4853,44 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>A failed run sets Status = Degraded and LastError, cleared on success. Corroborated by the Autotask 405 incident this run, which exercised the path for real - LastError reads empty now precisely because the next success cleared it.</t>
+          <t>Both connections healthy, enabled, synced within the minute, no error.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>9. Field Mapping</t>
+          <t>8. PSA Connections</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>MAP-01</t>
+          <t>CONN-14</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Mapping page lists live options</t>
+          <t>Failure marks the connection degraded</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/mappings, pick a connection and the status tab.</t>
+          <t>Temporarily point a connection at an unreachable endpoint and let a sync run.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Options come from live discovery, showing human labels.</t>
+          <t>Status becomes Failed/Degraded with the real reason in LastError, and the loop keeps running for the other connection.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>SQL + worker log.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>A failed run sets Status = Degraded and LastError, cleared on success. Corroborated by the Autotask 405 incident this run, which exercised the path for real - LastError reads empty now precisely because the next success cleared it.</t>
         </is>
       </c>
     </row>
@@ -4917,32 +4917,32 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>MAP-02</t>
+          <t>MAP-01</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>A saved rule matches an incoming ticket</t>
+          <t>Mapping page lists live options</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Save a status mapping through the UI, then force a re-sync.</t>
+          <t>Open /dashboard/mappings, pick a connection and the status tab.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Tickets in that status show the mapped PORTAL value.</t>
+          <t>Options come from live discovery, showing human labels.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "PsaStatus","PortalStatus" ... - THE KEY CHECK IS THAT THEY DIFFER. PsaStatus = PortalStatus on every row means nothing is mapping at all.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Zero raw statuses and zero raw priorities on both connections - PsaStatus differs from PortalStatus everywhere a rule exists.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -4969,27 +4969,27 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MAP-03</t>
+          <t>MAP-02</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Unmapped provider values are reported</t>
+          <t>A saved rule matches an incoming ticket</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Move a ticket in the PSA into a status with no rule, then sync.</t>
+          <t>Save a status mapping through the UI, then force a re-sync.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>The worker logs a warning naming provider, field and value, once per run.</t>
+          <t>Tickets in that status show the mapped PORTAL value.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>docker logs desk-portal-prod-worker-1 | grep 'No mapping rule matches'. Silence here used to mean the bug was invisible.</t>
+          <t>SQL: select "PsaStatus","PortalStatus" ... - THE KEY CHECK IS THAT THEY DIFFER. PsaStatus = PortalStatus on every row means nothing is mapping at all.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Unmapped values are named in the worker log; zero outstanding after the mappings were completed this run.</t>
+          <t>Zero raw statuses and zero raw priorities on both connections - PsaStatus differs from PortalStatus everywhere a rule exists.</t>
         </is>
       </c>
     </row>
@@ -5021,27 +5021,27 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>MAP-04</t>
+          <t>MAP-03</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Unmapped values fall through, they do not crash</t>
+          <t>Unmapped provider values are reported</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Same as MAP-03.</t>
+          <t>Move a ticket in the PSA into a status with no rule, then sync.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>The ticket still imports, carrying the provider's raw value.</t>
+          <t>The worker logs a warning naming provider, field and value, once per run.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>docker logs desk-portal-prod-worker-1 | grep 'No mapping rule matches'. Silence here used to mean the bug was invisible.</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>An unmapped value passes through and the ticket still imports.</t>
+          <t>Unmapped values are named in the worker log; zero outstanding after the mappings were completed this run.</t>
         </is>
       </c>
     </row>
@@ -5073,27 +5073,27 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>MAP-05</t>
+          <t>MAP-04</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Inbound ambiguity is prevented</t>
+          <t>Unmapped values fall through, they do not crash</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Run the ambiguity query after any mapping change: select "PsaConnectionId","PortalField","ExternalValue",count(*) from field_mappings where "IsActive" and "Direction" in (2,3) group by 1,2,3 having count(*)&gt;1;</t>
+          <t>Same as MAP-03.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Zero rows. Two inbound rules on one provider value resolve non-deterministically.</t>
+          <t>The ticket still imports, carrying the provider's raw value.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>SQL. Run the mirror query for outbound: Direction in (1,3) grouped by PortalValue.</t>
+          <t>SQL.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Zero rows from the inbound ambiguity query, and zero from its outbound mirror.</t>
+          <t>An unmapped value passes through and the ticket still imports.</t>
         </is>
       </c>
     </row>
@@ -5125,32 +5125,32 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>MAP-06</t>
+          <t>MAP-05</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Direction is honoured</t>
+          <t>Inbound ambiguity is prevented</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Create a ProviderToPortal-only rule and push a change from the portal.</t>
+          <t>Run the ambiguity query after any mapping change: select "PsaConnectionId","PortalField","ExternalValue",count(*) from field_mappings where "IsActive" and "Direction" in (2,3) group by 1,2,3 having count(*)&gt;1;</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>The inbound-only rule is not used outbound.</t>
+          <t>Zero rows. Two inbound rules on one provider value resolve non-deterministically.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>PSA UI - confirm the pushed value came from the bidirectional rule.</t>
+          <t>SQL. Run the mirror query for outbound: Direction in (1,3) grouped by PortalValue.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Needs a portal-side push.</t>
+          <t>Zero rows from the inbound ambiguity query, and zero from its outbound mirror.</t>
         </is>
       </c>
     </row>
@@ -5177,32 +5177,32 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>MAP-07</t>
+          <t>MAP-06</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Two portal values sharing one provider value</t>
+          <t>Direction is honoured</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Map RESOLVED and CLOSED both to the same provider status.</t>
+          <t>Create a ProviderToPortal-only rule and push a change from the portal.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Exactly one is Bidirectional and the other PortalToProvider, so inbound is deterministic.</t>
+          <t>The inbound-only rule is not used outbound.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>SQL + an inbound sync of a closed ticket.</t>
+          <t>PSA UI - confirm the pushed value came from the bidirectional rule.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Three provider values are each claimed by two portal values, and in every case exactly one rule is inbound-eligible.</t>
+          <t>Needs a portal-side push.</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5229,32 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>MAP-08</t>
+          <t>MAP-07</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Autotask numeric picklists resolve</t>
+          <t>Two portal values sharing one provider value</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Change a ticket status from the portal on an Autotask ticket.</t>
+          <t>Map RESOLVED and CLOSED both to the same provider status.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>The label is resolved to the numeric id before the write; no 'Could not convert string to integer' error.</t>
+          <t>Exactly one is Bidirectional and the other PortalToProvider, so inbound is deterministic.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + API response.</t>
+          <t>SQL + an inbound sync of a closed ticket.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Needs a portal-side status change.</t>
+          <t>Three provider values are each claimed by two portal values, and in every case exactly one rule is inbound-eligible.</t>
         </is>
       </c>
     </row>
@@ -5281,27 +5281,27 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>MAP-09</t>
+          <t>MAP-08</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ConnectWise board-scoped statuses</t>
+          <t>Autotask numeric picklists resolve</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Change status on ConnectWise tickets that live on different boards.</t>
+          <t>Change a ticket status from the portal on an Autotask ticket.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>The status name resolves against each ticket's OWN board.</t>
+          <t>The label is resolved to the numeric id before the write; no 'Could not convert string to integer' error.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>PSA UI. An id from another board must produce a clear error naming the available statuses.</t>
+          <t>PSA UI + API response.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -5333,27 +5333,27 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>MAP-10</t>
+          <t>MAP-09</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Statuses from every board are offered</t>
+          <t>ConnectWise board-scoped statuses</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>On ConnectWise, confirm the status dropdown includes a status that exists only on a second board.</t>
+          <t>Change status on ConnectWise tickets that live on different boards.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Present. Reading only the first board hides statuses tickets genuinely arrive in.</t>
+          <t>The status name resolves against each ticket's OWN board.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>PSA UI. An id from another board must produce a clear error naming the available statuses.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Needs the mapping page.</t>
+          <t>Needs a portal-side status change.</t>
         </is>
       </c>
     </row>
@@ -5385,27 +5385,27 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>MAP-11</t>
+          <t>MAP-10</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Queue and category mapping</t>
+          <t>Statuses from every board are offered</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Map a provider queue name to a different portal name and re-sync.</t>
+          <t>On ConnectWise, confirm the status dropdown includes a status that exists only on a second board.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Tickets display the portal name.</t>
+          <t>Present. Reading only the first board hides statuses tickets genuinely arrive in.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>SQL on tickets."QueueOrBoard".</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -5437,32 +5437,32 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>MAP-12</t>
+          <t>MAP-11</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Mapping change reaches tickets already imported</t>
+          <t>Queue and category mapping</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Change a queue or status mapping, then force a re-sync.</t>
+          <t>Map a provider queue name to a different portal name and re-sync.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>EXISTING tickets update, not only new ones.</t>
+          <t>Tickets display the portal name.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>SQL before/after. If nothing changes, the field is missing from the update hash - that exact bug has occurred three times.</t>
+          <t>SQL on tickets."QueueOrBoard".</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Re-pointing two queue rules moved 124 tickets once the queue joined the update hash - which is how that gap was found.</t>
+          <t>Needs the mapping page.</t>
         </is>
       </c>
     </row>
@@ -5489,32 +5489,32 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>MAP-13</t>
+          <t>MAP-12</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Version snapshot and rollback</t>
+          <t>Mapping change reaches tickets already imported</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Change a mapping, then GET /api/admin/mappings/versions and roll back.</t>
+          <t>Change a queue or status mapping, then force a re-sync.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>The prior rule set is restored exactly.</t>
+          <t>EXISTING tickets update, not only new ones.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>API + SQL. field_mapping_versions.SnapshotJson is also the recovery path after a bad direct SQL edit.</t>
+          <t>SQL before/after. If nothing changes, the field is missing from the update hash - that exact bug has occurred three times.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session.</t>
+          <t>Re-pointing two queue rules moved 124 tickets once the queue joined the update hash - which is how that gap was found.</t>
         </is>
       </c>
     </row>
@@ -5541,32 +5541,32 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>MAP-14</t>
+          <t>MAP-13</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Direct SQL edits must be connection-scoped</t>
+          <t>Version snapshot and rollback</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>If editing mappings in SQL, always include PsaConnectionId and check the reported row count against what you expected.</t>
+          <t>Change a mapping, then GET /api/admin/mappings/versions and roll back.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Row count matches expectation exactly.</t>
+          <t>The prior rule set is restored exactly.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>psql. An UPDATE without PsaConnectionId hits BOTH connections - this has happened.</t>
+          <t>API + SQL. field_mapping_versions.SnapshotJson is also the recovery path after a bad direct SQL edit.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Every direct edit this run was scoped by PsaConnectionId and its row count checked against what was expected.</t>
+          <t>Needs an admin session.</t>
         </is>
       </c>
     </row>
@@ -5593,32 +5593,32 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>MAP-15</t>
+          <t>MAP-14</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Work type mapping</t>
+          <t>Direct SQL edits must be connection-scoped</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Map a portal work type to a provider work type and log time using it.</t>
+          <t>If editing mappings in SQL, always include PsaConnectionId and check the reported row count against what you expected.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>The PSA time entry carries the mapped work type.</t>
+          <t>Row count matches expectation exactly.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>PSA UI.</t>
+          <t>psql. An UPDATE without PsaConnectionId hits BOTH connections - this has happened.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Needs a session to log time.</t>
+          <t>Every direct edit this run was scoped by PsaConnectionId and its row count checked against what was expected.</t>
         </is>
       </c>
     </row>
@@ -5645,32 +5645,32 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MAP-16</t>
+          <t>MAP-15</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Mapping rules take effect without a restart</t>
+          <t>Work type mapping</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Edit a rule in the database, then wait for the next sync tick.</t>
+          <t>Map a portal work type to a provider work type and log time using it.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>The new rule applies - rules are read fresh from the database each run, with no cache.</t>
+          <t>The PSA time entry carries the mapped work type.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>SQL + worker behaviour. Note such edits bypass the version snapshot and audit trail.</t>
+          <t>PSA UI.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5685,39 +5685,39 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Rules edited in the database took effect on the next tick with no restart.</t>
+          <t>Needs a session to log time.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>10. Ticket Sync Engine</t>
+          <t>9. Field Mapping</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>SYNC-01</t>
+          <t>MAP-16</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>First import creates tickets and companies</t>
+          <t>Mapping rules take effect without a restart</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Point a connection at a PSA with tickets and run a full sync.</t>
+          <t>Edit a rule in the database, then wait for the next sync tick.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Tickets imported and client companies auto-created for unknown company ids.</t>
+          <t>The new rule applies - rules are read fresh from the database each run, with no cache.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>SQL counts on tickets and client_companies.</t>
+          <t>SQL + worker behaviour. Note such edits bypass the version snapshot and audit trail.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Seven Autotask and four ConnectWise companies auto-created, all carrying tickets.</t>
+          <t>Rules edited in the database took effect on the next tick with no restart.</t>
         </is>
       </c>
     </row>
@@ -5749,27 +5749,27 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>SYNC-02</t>
+          <t>SYNC-01</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Pagination reads past the first page</t>
+          <t>First import creates tickets and companies</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Ensure the PSA has more tickets in range than the page size (100), then force a full re-sync with: update psa_connections set "LastSuccessfulSyncAt"=NULL;</t>
+          <t>Point a connection at a PSA with tickets and run a full sync.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>ALL tickets import, not the first 100. Autotask follows nextPageUrl; ConnectWise pages by number ordered by id.</t>
+          <t>Tickets imported and client companies auto-created for unknown company ids.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>SQL count vs the PSA's own count. This bug silently cost 34 of 135 tickets.</t>
+          <t>SQL counts on tickets and client_companies.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>A full re-sync fetched 135 across two pages plus a next-page call. Before the fix it stopped at 100 and reported success.</t>
+          <t>Seven Autotask and four ConnectWise companies auto-created, all carrying tickets.</t>
         </is>
       </c>
     </row>
@@ -5801,27 +5801,27 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>SYNC-03</t>
+          <t>SYNC-02</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Page boundaries do not skip or duplicate</t>
+          <t>Pagination reads past the first page</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>After SYNC-02, check for duplicates.</t>
+          <t>Ensure the PSA has more tickets in range than the page size (100), then force a full re-sync with: update psa_connections set "LastSuccessfulSyncAt"=NULL;</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>select "ExternalTicketId",count(*) from tickets group by 1 having count(*)&gt;1 returns nothing, and the total matches the PSA.</t>
+          <t>ALL tickets import, not the first 100. Autotask follows nextPageUrl; ConnectWise pages by number ordered by id.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>SQL count vs the PSA's own count. This bug silently cost 34 of 135 tickets.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Zero duplicate (connection, external id) pairs.</t>
+          <t>A full re-sync fetched 135 across two pages plus a next-page call. Before the fix it stopped at 100 and reported success.</t>
         </is>
       </c>
     </row>
@@ -5853,27 +5853,27 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>SYNC-04</t>
+          <t>SYNC-03</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Page cap is reported, not silent</t>
+          <t>Page boundaries do not skip or duplicate</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>If a run hits the 50-page safety cap, the worker warns.</t>
+          <t>After SYNC-02, check for duplicates.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>A warning naming the connection appears; the run is known to be incomplete.</t>
+          <t>select "ExternalTicketId",count(*) from tickets group by 1 having count(*)&gt;1 returns nothing, and the total matches the PSA.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>grep 'safety cap' in the worker log.</t>
+          <t>SQL.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Zero page-cap warnings; headroom is 2.7% of the ceiling.</t>
+          <t>Zero duplicate (connection, external id) pairs.</t>
         </is>
       </c>
     </row>
@@ -5905,27 +5905,27 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>SYNC-05</t>
+          <t>SYNC-04</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Unchanged ticket is skipped</t>
+          <t>Page cap is reported, not silent</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Run two syncs back to back with no PSA changes.</t>
+          <t>If a run hits the 50-page safety cap, the worker warns.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>The second reports no updates - the update hash short-circuits.</t>
+          <t>A warning naming the connection appears; the run is known to be incomplete.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Worker log / sync result.</t>
+          <t>grep 'safety cap' in the worker log.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Quiet cycles report no work and cost about three requests.</t>
+          <t>Zero page-cap warnings; headroom is 2.7% of the ceiling.</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>SYNC-06</t>
+          <t>SYNC-05</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>A changed field always reaches an existing row</t>
+          <t>Unchanged ticket is skipped</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Change ONE field in the PSA (status, priority, title, queue, or a date) and sync.</t>
+          <t>Run two syncs back to back with no PSA changes.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>The portal row updates. Every field the sync writes must be in the state hash.</t>
+          <t>The second reports no updates - the update hash short-circuits.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>SQL per field. Test the queue and the lifecycle dates specifically - both have failed here.</t>
+          <t>Worker log / sync result.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Needs a field-only edit in the PSA the connector actually reads. Two attempts this run never reached the instance in question.</t>
+          <t>Quiet cycles report no work and cost about three requests.</t>
         </is>
       </c>
     </row>
@@ -6009,27 +6009,27 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>SYNC-07</t>
+          <t>SYNC-06</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Portal echo is suppressed</t>
+          <t>A changed field always reaches an existing row</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Change a status from the portal, then let the next sync run.</t>
+          <t>Change ONE field in the PSA (status, priority, title, queue, or a date) and sync.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>The change coming back from the PSA is recognised as our own and does not re-trigger an update or a duplicate activity event.</t>
+          <t>The portal row updates. Every field the sync writes must be in the state hash.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>SQL on sync_events + activity_events counts.</t>
+          <t>SQL per field. Test the queue and the lifecycle dates specifically - both have failed here.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Needs a portal-side write.</t>
+          <t>Needs a field-only edit in the PSA the connector actually reads. Two attempts this run never reached the instance in question.</t>
         </is>
       </c>
     </row>
@@ -6061,32 +6061,32 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>SYNC-08</t>
+          <t>SYNC-07</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Lifecycle dates are captured</t>
+          <t>Portal echo is suppressed</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sync tickets that are open, resolved and closed.</t>
+          <t>Change a status from the portal, then let the next sync run.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>PsaCreatedAt (raise date), ResolvedAt, ClosedAt and SlaDueAt populate where the provider supplies them.</t>
+          <t>The change coming back from the PSA is recognised as our own and does not re-trigger an update or a duplicate activity event.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>SQL: select count(*), count("PsaCreatedAt"), count("ClosedAt"), count("SlaDueAt") from tickets.</t>
+          <t>SQL on sync_events + activity_events counts.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Autotask 135/135 raise dates, 135 SLA, 113 closures; ConnectWise 13/13 raise and SLA.</t>
+          <t>Needs a portal-side write.</t>
         </is>
       </c>
     </row>
@@ -6113,27 +6113,27 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>SYNC-09</t>
+          <t>SYNC-08</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Raise date is the PSA date, not the import date</t>
+          <t>Lifecycle dates are captured</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Compare PsaCreatedAt with the ticket's created date in the PSA.</t>
+          <t>Sync tickets that are open, resolved and closed.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>They match. The row's own CreatedAt is the import time and must not be used as ticket age.</t>
+          <t>PsaCreatedAt (raise date), ResolvedAt, ClosedAt and SlaDueAt populate where the provider supplies them.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>SQL vs PSA UI.</t>
+          <t>SQL: select count(*), count("PsaCreatedAt"), count("ClosedAt"), count("SlaDueAt") from tickets.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Raise dates span July to September - the PSA date, not the import date.</t>
+          <t>Autotask 135/135 raise dates, 135 SLA, 113 closures; ConnectWise 13/13 raise and SLA.</t>
         </is>
       </c>
     </row>
@@ -6165,27 +6165,27 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>SYNC-10</t>
+          <t>SYNC-09</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Absent is distinguished from empty</t>
+          <t>Raise date is the PSA date, not the import date</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Check a ConnectWise open ticket.</t>
+          <t>Compare PsaCreatedAt with the ticket's created date in the PSA.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>ClosedAt is null because the provider omits the field while the ticket is open - not because the mapping is wrong. Do not fill it with lastUpdated.</t>
+          <t>They match. The row's own CreatedAt is the import time and must not be used as ticket age.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>SQL + the connector's field-shape log line.</t>
+          <t>SQL vs PSA UI.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>ConnectWise sends no closure date because no board status is flagged as closing - confirmed by closedFlag being false on all six tickets sitting in Completed. Absent, not mis-mapped.</t>
+          <t>Raise dates span July to September - the PSA date, not the import date.</t>
         </is>
       </c>
     </row>
@@ -6217,27 +6217,27 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>SYNC-11</t>
+          <t>SYNC-10</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Notes import both ways</t>
+          <t>Absent is distinguished from empty</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Add a public and an internal note in the PSA, then sync.</t>
+          <t>Check a ConnectWise open ticket.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Both import with the correct IsPublic flag and author side.</t>
+          <t>ClosedAt is null because the provider omits the field while the ticket is open - not because the mapping is wrong. Do not fill it with lastUpdated.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Portal thread + SQL on ticket_notes.</t>
+          <t>SQL + the connector's field-shape log line.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>355 notes imported, 216 internal and 139 public.</t>
+          <t>ConnectWise sends no closure date because no board status is flagged as closing - confirmed by closedFlag being false on all six tickets sitting in Completed. Absent, not mis-mapped.</t>
         </is>
       </c>
     </row>
@@ -6269,27 +6269,27 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>SYNC-12</t>
+          <t>SYNC-11</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Time-entry notes are included</t>
+          <t>Notes import both ways</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Add a note on a PSA time entry.</t>
+          <t>Add a public and an internal note in the PSA, then sync.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>It appears in the portal thread as internal, keyed te-{id}.</t>
+          <t>Both import with the correct IsPublic flag and author side.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Portal thread.</t>
+          <t>Portal thread + SQL on ticket_notes.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Time-entry notes import as internal.</t>
+          <t>355 notes imported, 216 internal and 139 public.</t>
         </is>
       </c>
     </row>
@@ -6321,32 +6321,32 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>SYNC-13</t>
+          <t>SYNC-12</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Deletion reconciliation</t>
+          <t>Time-entry notes are included</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Delete a note in the PSA and sync.</t>
+          <t>Add a note on a PSA time entry.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>The portal removes it - but only provider-origin notes; portal-authored notes are never reconciled away.</t>
+          <t>It appears in the portal thread as internal, keyed te-{id}.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>SQL on ticket_notes before/after.</t>
+          <t>Portal thread.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Needs a note deleted in the PSA.</t>
+          <t>Time-entry notes import as internal.</t>
         </is>
       </c>
     </row>
@@ -6373,32 +6373,32 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>SYNC-14</t>
+          <t>SYNC-13</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Unsynced tickets are visible and re-syncable</t>
+          <t>Deletion reconciliation</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/tickets/unsynced, then POST /api/admin/tickets/{id}/resync.</t>
+          <t>Delete a note in the PSA and sync.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Failed rows are listed with their error and can be retried individually.</t>
+          <t>The portal removes it - but only provider-origin notes; portal-authored notes are never reconciled away.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Browser + API.</t>
+          <t>SQL on ticket_notes before/after.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Every ticket carries a synced status; none failed.</t>
+          <t>Needs a note deleted in the PSA.</t>
         </is>
       </c>
     </row>
@@ -6425,27 +6425,27 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>SYNC-15</t>
+          <t>SYNC-14</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>A failing connection does not stop the other</t>
+          <t>Unsynced tickets are visible and re-syncable</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Break connection A's credentials and let a cycle run.</t>
+          <t>GET /api/admin/tickets/unsynced, then POST /api/admin/tickets/{id}/resync.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Connection B still syncs; A is marked with its error.</t>
+          <t>Failed rows are listed with their error and can be retried individually.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Worker log + SQL.</t>
+          <t>Browser + API.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Zero sync failures across the run; a failing connection was never induced deliberately on production.</t>
+          <t>Every ticket carries a synced status; none failed.</t>
         </is>
       </c>
     </row>
@@ -6477,27 +6477,27 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>SYNC-16</t>
+          <t>SYNC-15</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Sync completion signal</t>
+          <t>A failing connection does not stop the other</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>To confirm a sync ran, watch psa_connections."LastSuccessfulSyncAt" move.</t>
+          <t>Break connection A's credentials and let a cycle run.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>The timestamp advances. Do NOT poll the log for a 'Synced ...' line: it is only written when something changed, and docker logs --since still contains earlier runs.</t>
+          <t>Connection B still syncs; A is marked with its error.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>SQL. This exact mistake produced three false verifications in one day.</t>
+          <t>Worker log + SQL.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -6517,49 +6517,61 @@
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>LastSuccessfulSyncAt advancing is the reliable signal; the summary log line is written only when something changed.</t>
+          <t>Zero sync failures across the run; a failing connection was never induced deliberately on production.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>11. Ticket Lifecycle in the Portal</t>
+          <t>10. Ticket Sync Engine</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>TKT-01</t>
+          <t>SYNC-16</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ticket list and filters</t>
+          <t>Sync completion signal</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/tickets and filter by status, queue, technician and unassigned.</t>
+          <t>To confirm a sync ran, watch psa_connections."LastSuccessfulSyncAt" move.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Counts match SQL for the same filter.</t>
+          <t>The timestamp advances. Do NOT poll the log for a 'Synced ...' line: it is only written when something changed, and docker logs --since still contains earlier runs.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>SQL. This exact mistake produced three false verifications in one day.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>LastSuccessfulSyncAt advancing is the reliable signal; the summary log line is written only when something changed.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6569,27 +6581,27 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>TKT-02</t>
+          <t>TKT-01</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ticket detail renders fully</t>
+          <t>Ticket list and filters</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket with notes, time entries and attachments.</t>
+          <t>Open /dashboard/tickets and filter by status, queue, technician and unassigned.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Properties rail, conversation, time panel and attachments all render, no console errors.</t>
+          <t>Counts match SQL for the same filter.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Browser DevTools console.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -6609,27 +6621,27 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>TKT-03</t>
+          <t>TKT-02</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Create a ticket from the portal</t>
+          <t>Ticket detail renders fully</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>/dashboard/tickets/new, fill required fields, submit.</t>
+          <t>Open a ticket with notes, time entries and attachments.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Created in the PSA FIRST, then stored locally with the returned external id.</t>
+          <t>Properties rail, conversation, time panel and attachments all render, no console errors.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + SQL: "ExternalTicketId" is populated, not null.</t>
+          <t>Browser DevTools console.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -6649,27 +6661,27 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>TKT-04</t>
+          <t>TKT-03</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Status change pushes to the PSA</t>
+          <t>Create a ticket from the portal</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>POST /api/tickets/{id}/status or use the UI control.</t>
+          <t>/dashboard/tickets/new, fill required fields, submit.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>The PSA reflects the new status; the portal shows the mapped value.</t>
+          <t>Created in the PSA FIRST, then stored locally with the returned external id.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>PSA UI. Then let a sync run and confirm it is not re-applied as an inbound change.</t>
+          <t>PSA UI + SQL: "ExternalTicketId" is populated, not null.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -6689,27 +6701,27 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>TKT-05</t>
+          <t>TKT-04</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Rejected status change surfaces the real reason</t>
+          <t>Status change pushes to the PSA</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Attempt a status the PSA will refuse (for example one from another board).</t>
+          <t>POST /api/tickets/{id}/status or use the UI control.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>The provider's own message is shown, not 'Still rejected' or a generic error, and the stored error is from THIS attempt, not the previous one.</t>
+          <t>The PSA reflects the new status; the portal shows the mapped value.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Browser. Compare the row's UpdatedAt with the time of your attempt.</t>
+          <t>PSA UI. Then let a sync run and confirm it is not re-applied as an inbound change.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6729,27 +6741,27 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>TKT-06</t>
+          <t>TKT-05</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Rejected status change surfaces the real reason</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>GET /api/tickets/{id}/assignees then PUT /api/tickets/{id}/assignment.</t>
+          <t>Attempt a status the PSA will refuse (for example one from another board).</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Only technicians who cover that queue are offered; the PSA is updated.</t>
+          <t>The provider's own message is shown, not 'Still rejected' or a generic error, and the stored error is from THIS attempt, not the previous one.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>PSA UI.</t>
+          <t>Browser. Compare the row's UpdatedAt with the time of your attempt.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -6769,27 +6781,27 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>TKT-07</t>
+          <t>TKT-06</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Service instructions surface</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Set account-level instructions in the Control Panel, then open a ticket for that account.</t>
+          <t>GET /api/tickets/{id}/assignees then PUT /api/tickets/{id}/assignment.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>The amber instructions panel shows the account override, falling back to the global text.</t>
+          <t>Only technicians who cover that queue are offered; the PSA is updated.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>PSA UI.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -6809,27 +6821,27 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>TKT-08</t>
+          <t>TKT-07</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Ticket page hides staff tooling from clients</t>
+          <t>Service instructions surface</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Open the same ticket as a client user.</t>
+          <t>Set account-level instructions in the Control Panel, then open a ticket for that account.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Time panel, assignment and status controls absent; the time query is not even issued.</t>
+          <t>The amber instructions panel shows the account override, falling back to the global text.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Browser network tab.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -6849,27 +6861,27 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>TKT-09</t>
+          <t>TKT-08</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>SLA and dates display</t>
+          <t>Ticket page hides staff tooling from clients</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket with an SLA target.</t>
+          <t>Open the same ticket as a client user.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Raise date, SLA due and closure date display and match the PSA.</t>
+          <t>Time panel, assignment and status controls absent; the time query is not even issued.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Browser vs PSA UI.</t>
+          <t>Browser network tab.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -6889,27 +6901,27 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>TKT-10</t>
+          <t>TKT-09</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Queue change in the PSA reaches the portal</t>
+          <t>SLA and dates display</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Move a ticket to another queue in the PSA, changing nothing else, then sync.</t>
+          <t>Open a ticket with an SLA target.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>The portal shows the new queue.</t>
+          <t>Raise date, SLA due and closure date display and match the PSA.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>SQL. This silently failed until the queue joined the update hash.</t>
+          <t>Browser vs PSA UI.</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -6929,27 +6941,27 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>TKT-11</t>
+          <t>TKT-10</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Concurrent edit does not lose data</t>
+          <t>Queue change in the PSA reaches the portal</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Change a ticket in the PSA and in the portal at nearly the same time, then sync.</t>
+          <t>Move a ticket to another queue in the PSA, changing nothing else, then sync.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>No lost update and no infinite echo loop.</t>
+          <t>The portal shows the new queue.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>SQL + worker log.</t>
+          <t>SQL. This silently failed until the queue joined the update hash.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -6969,27 +6981,27 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>TKT-12</t>
+          <t>TKT-11</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Ticket search</t>
+          <t>Concurrent edit does not lose data</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Use the header search for a ticket reference and a keyword.</t>
+          <t>Change a ticket in the PSA and in the portal at nearly the same time, then sync.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Correct results, scoped to what the user may see.</t>
+          <t>No lost update and no infinite echo loop.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Browser as two different roles.</t>
+          <t>SQL + worker log.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -7009,27 +7021,27 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>TKT-13</t>
+          <t>TKT-12</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Reply composer keeps a draft</t>
+          <t>Ticket search</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Type a reply, close the dialog, reopen it.</t>
+          <t>Use the header search for a ticket reference and a keyword.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>The draft text is preserved and the launcher shows a draft-in-progress badge.</t>
+          <t>Correct results, scoped to what the user may see.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser as two different roles.</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -7049,27 +7061,27 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>TKT-14</t>
+          <t>TKT-13</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Failed send keeps the draft</t>
+          <t>Reply composer keeps a draft</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Disconnect the network, send a reply, then reconnect.</t>
+          <t>Type a reply, close the dialog, reopen it.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>The dialog stays open with the text intact; it closes only on success.</t>
+          <t>The draft text is preserved and the launcher shows a draft-in-progress badge.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Browser DevTools offline mode.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -7084,32 +7096,32 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>12. Notes, Conversation and Recipients</t>
+          <t>11. Ticket Lifecycle in the Portal</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>NOTE-01</t>
+          <t>TKT-14</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Public reply reaches the PSA and the client</t>
+          <t>Failed send keeps the draft</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Post a public reply as staff.</t>
+          <t>Disconnect the network, send a reply, then reconnect.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Appears in the PSA as a public note and is visible to the client user.</t>
+          <t>The dialog stays open with the text intact; it closes only on success.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + client session.</t>
+          <t>Browser DevTools offline mode.</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -7129,27 +7141,27 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>NOTE-02</t>
+          <t>NOTE-01</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Internal note stays internal</t>
+          <t>Public reply reaches the PSA and the client</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Post an internal note.</t>
+          <t>Post a public reply as staff.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Marked internal in the PSA, shown with the amber internal badge to staff, and absent from the client payload.</t>
+          <t>Appears in the PSA as a public note and is visible to the client user.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Raw JSON in a client session - not just the UI.</t>
+          <t>PSA UI + client session.</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -7169,27 +7181,27 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>NOTE-03</t>
+          <t>NOTE-02</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Autotask internal-only text is preserved</t>
+          <t>Internal note stays internal</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>In Autotask, create a time entry with text in Internal Notes only, then sync.</t>
+          <t>Post an internal note.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>The internal text is imported, not dropped, and a pointer-only summary such as 'See Internal Notes' is not duplicated.</t>
+          <t>Marked internal in the PSA, shown with the amber internal badge to staff, and absent from the client payload.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Portal thread vs Autotask.</t>
+          <t>Raw JSON in a client session - not just the UI.</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -7209,27 +7221,27 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>NOTE-04</t>
+          <t>NOTE-03</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Note title is not duplicated into the body</t>
+          <t>Autotask internal-only text is preserved</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Post a long note to Autotask from the portal.</t>
+          <t>In Autotask, create a time entry with text in Internal Notes only, then sync.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Autotask shows it once. The title is truncated on a word boundary, not the first 250 characters of the body.</t>
+          <t>The internal text is imported, not dropped, and a pointer-only summary such as 'See Internal Notes' is not duplicated.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Autotask UI. The symptom of the old bug was 'we sent one note but Autotask shows two'.</t>
+          <t>Portal thread vs Autotask.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -7249,27 +7261,27 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>NOTE-05</t>
+          <t>NOTE-04</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>To and Cc on a public reply</t>
+          <t>Note title is not duplicated into the body</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>GET /api/tickets/{id}/recipients, choose contacts, send.</t>
+          <t>Post a long note to Autotask from the portal.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Only contacts belonging to that ticket's company are offered, and the email goes to the chosen recipients.</t>
+          <t>Autotask shows it once. The title is truncated on a word boundary, not the first 250 characters of the body.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>API + PSA UI. Confirm no contact from another company can be selected.</t>
+          <t>Autotask UI. The symptom of the old bug was 'we sent one note but Autotask shows two'.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -7289,27 +7301,27 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>NOTE-06</t>
+          <t>NOTE-05</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Recipient support degrades cleanly</t>
+          <t>To and Cc on a public reply</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Send a public reply on an Autotask ticket.</t>
+          <t>GET /api/tickets/{id}/recipients, choose contacts, send.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Autotask does not support note email recipients - the UI reflects that rather than silently dropping the selection.</t>
+          <t>Only contacts belonging to that ticket's company are offered, and the email goes to the chosen recipients.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>API + PSA UI. Confirm no contact from another company can be selected.</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -7329,22 +7341,22 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>NOTE-07</t>
+          <t>NOTE-06</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Conversation shows newest first with Show all</t>
+          <t>Recipient support degrades cleanly</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket with more than four notes.</t>
+          <t>Send a public reply on an Autotask ticket.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>The four most recent show, newest first, with a Show all button revealing the rest.</t>
+          <t>Autotask does not support note email recipients - the UI reflects that rather than silently dropping the selection.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7369,22 +7381,22 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>NOTE-08</t>
+          <t>NOTE-07</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Note kinds are visually distinct</t>
+          <t>Conversation shows newest first with Show all</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>View a thread with client, staff, internal and time-entry notes.</t>
+          <t>Open a ticket with more than four notes.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Each kind is visually distinguishable.</t>
+          <t>The four most recent show, newest first, with a Show all button revealing the rest.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7409,27 +7421,27 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>NOTE-09</t>
+          <t>NOTE-08</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Time on a reply is linked to its note</t>
+          <t>Note kinds are visually distinct</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Send a reply with time logged in one action.</t>
+          <t>View a thread with client, staff, internal and time-entry notes.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>The time entry is linked to that note (NoteId) and the staff thread shows the duration on the reply.</t>
+          <t>Each kind is visually distinguishable.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "NoteId" from ticket_time_entries order by "CreatedAt" desc limit 1.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -7449,27 +7461,27 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>NOTE-10</t>
+          <t>NOTE-09</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Note ordering and timestamps</t>
+          <t>Time on a reply is linked to its note</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Compare the thread order with the PSA.</t>
+          <t>Send a reply with time logged in one action.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Chronology matches; timestamps are the provider's, not the import time.</t>
+          <t>The time entry is linked to that note (NoteId) and the staff thread shows the duration on the reply.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Browser vs PSA UI.</t>
+          <t>SQL: select "NoteId" from ticket_time_entries order by "CreatedAt" desc limit 1.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -7484,32 +7496,32 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>13. Time Tracking</t>
+          <t>12. Notes, Conversation and Recipients</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>TIME-01</t>
+          <t>NOTE-10</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Log time on a ticket</t>
+          <t>Note ordering and timestamps</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Time panel &gt; log 0.5h with notes, billable.</t>
+          <t>Compare the thread order with the PSA.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Created in the PSA and listed in the portal with matching duration.</t>
+          <t>Chronology matches; timestamps are the provider's, not the import time.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + portal panel.</t>
+          <t>Browser vs PSA UI.</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -7529,27 +7541,27 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>TIME-02</t>
+          <t>TIME-01</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Fractional hours are accepted</t>
+          <t>Log time on a ticket</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Log 0.25h and 0.30h (18 minutes).</t>
+          <t>Time panel &gt; log 0.5h with notes, billable.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Both accepted. The input step must not block them.</t>
+          <t>Created in the PSA and listed in the portal with matching duration.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Browser. An HTML step of 0.25 silently blocked 18-minute entries.</t>
+          <t>PSA UI + portal panel.</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -7569,27 +7581,27 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>TIME-03</t>
+          <t>TIME-02</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Autotask requires summary notes</t>
+          <t>Fractional hours are accepted</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Attempt to log time on Autotask with an empty note.</t>
+          <t>Log 0.25h and 0.30h (18 minutes).</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>The UI marks Notes required and blocks submit. If a blank still arrives, a factual placeholder is sent rather than losing the time.</t>
+          <t>Both accepted. The input step must not block them.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Browser + PSA UI.</t>
+          <t>Browser. An HTML step of 0.25 silently blocked 18-minute entries.</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -7609,27 +7621,27 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>TIME-04</t>
+          <t>TIME-03</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Resource and role pairing</t>
+          <t>Autotask requires summary notes</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Configure a technician and a role that the technician does NOT hold, then log time.</t>
+          <t>Attempt to log time on Autotask with an empty note.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>The connector uses a role the technician actually holds rather than failing; if they hold none, a clear setup error is returned.</t>
+          <t>The UI marks Notes required and blocks submit. If a blank still arrives, a factual placeholder is sent rather than losing the time.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + API message.</t>
+          <t>Browser + PSA UI.</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -7649,27 +7661,27 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>TIME-05</t>
+          <t>TIME-04</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Missing time-entry resource is explained</t>
+          <t>Resource and role pairing</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Clear DefaultTimeEntryResourceId on an Autotask connection and log time.</t>
+          <t>Configure a technician and a role that the technician does NOT hold, then log time.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>A clear message telling the admin where to set it - not a raw 500.</t>
+          <t>The connector uses a role the technician actually holds rather than failing; if they hold none, a clear setup error is returned.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>PSA UI + API message.</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -7689,27 +7701,27 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>TIME-06</t>
+          <t>TIME-05</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Retry surfaces the current error</t>
+          <t>Missing time-entry resource is explained</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Fail a time entry, fix the configuration, then retry via POST /api/tickets/{id}/time/{entryId}/retry.</t>
+          <t>Clear DefaultTimeEntryResourceId on an Autotask connection and log time.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>The message shown is from THIS attempt. A stale error from the first failure is a defect.</t>
+          <t>A clear message telling the admin where to set it - not a raw 500.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Compare the row's UpdatedAt with the retry time.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -7729,27 +7741,27 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>TIME-07</t>
+          <t>TIME-06</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Edit a time entry</t>
+          <t>Retry surfaces the current error</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/tickets/{id}/time/{entryId}.</t>
+          <t>Fail a time entry, fix the configuration, then retry via POST /api/tickets/{id}/time/{entryId}/retry.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>The PSA entry updates and the portal aggregate is RECOMPUTED from the PSA, not adjusted locally.</t>
+          <t>The message shown is from THIS attempt. A stale error from the first failure is a defect.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>PSA UI + portal totals.</t>
+          <t>Compare the row's UpdatedAt with the retry time.</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -7769,22 +7781,22 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>TIME-08</t>
+          <t>TIME-07</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Delete a time entry</t>
+          <t>Edit a time entry</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/tickets/{id}/time/{entryId}.</t>
+          <t>PUT /api/tickets/{id}/time/{entryId}.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Removed in the PSA and the aggregate recomputed.</t>
+          <t>The PSA entry updates and the portal aggregate is RECOMPUTED from the PSA, not adjusted locally.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -7809,27 +7821,27 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>TIME-09</t>
+          <t>TIME-08</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Work type and role options</t>
+          <t>Delete a time entry</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>GET /api/tickets/{id}/time-options.</t>
+          <t>DELETE /api/tickets/{id}/time/{entryId}.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Only work types and roles valid for this connection and technician are offered.</t>
+          <t>Removed in the PSA and the aggregate recomputed.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>API.</t>
+          <t>PSA UI + portal totals.</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -7849,27 +7861,27 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>TIME-10</t>
+          <t>TIME-09</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Global timer</t>
+          <t>Work type and role options</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Start the header timer, attach it to a ticket, navigate away, return, then log it.</t>
+          <t>GET /api/tickets/{id}/time-options.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>The timer survives navigation and a page reload, and logs the elapsed time.</t>
+          <t>Only work types and roles valid for this connection and technician are offered.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Browser (state is persisted in localStorage).</t>
+          <t>API.</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -7889,27 +7901,27 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>TIME-11</t>
+          <t>TIME-10</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Time logged in the PSA reaches the portal</t>
+          <t>Global timer</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Add a time entry directly in the PSA, then sync.</t>
+          <t>Start the header timer, attach it to a ticket, navigate away, return, then log it.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Portal totals update. Time refresh is keyed off the ticket being FETCHED, not off the upsert reporting a change - a time entry changes no hashed field.</t>
+          <t>The timer survives navigation and a page reload, and logs the elapsed time.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Portal totals + SQL.</t>
+          <t>Browser (state is persisted in localStorage).</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -7929,27 +7941,27 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>TIME-12</t>
+          <t>TIME-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Client never sees time</t>
+          <t>Time logged in the PSA reaches the portal</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>View a ticket with time entries as a client user.</t>
+          <t>Add a time entry directly in the PSA, then sync.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>No time data in the payload at all.</t>
+          <t>Portal totals update. Time refresh is keyed off the ticket being FETCHED, not off the upsert reporting a change - a time entry changes no hashed field.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Raw JSON.</t>
+          <t>Portal totals + SQL.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -7969,27 +7981,27 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>TIME-13</t>
+          <t>TIME-12</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Permission gating</t>
+          <t>Client never sees time</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Attempt to log time as a role without tickets.time.log.</t>
+          <t>View a ticket with time entries as a client user.</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Refused, and the panel is not offered.</t>
+          <t>No time data in the payload at all.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Browser + API 403.</t>
+          <t>Raw JSON.</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -8009,27 +8021,27 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>TIME-14</t>
+          <t>TIME-13</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Billable flag round trip</t>
+          <t>Permission gating</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Log billable and non-billable entries.</t>
+          <t>Attempt to log time as a role without tickets.time.log.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Both are reflected correctly in the PSA.</t>
+          <t>Refused, and the panel is not offered.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>PSA UI.</t>
+          <t>Browser + API 403.</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -8044,32 +8056,32 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>14. Attachments</t>
+          <t>13. Time Tracking</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ATT-01</t>
+          <t>TIME-14</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Staff upload</t>
+          <t>Billable flag round trip</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Attach a file to a ticket from the dashboard.</t>
+          <t>Log billable and non-billable entries.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Uploads successfully and appears in the list.</t>
+          <t>Both are reflected correctly in the PSA.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Browser. The staff path was once client-only and every staff attach failed with 'Couldn't send'.</t>
+          <t>PSA UI.</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -8089,27 +8101,27 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ATT-02</t>
+          <t>ATT-01</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Client upload</t>
+          <t>Staff upload</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Attach a file as a client user.</t>
+          <t>Attach a file to a ticket from the dashboard.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Uploads and is visible to staff.</t>
+          <t>Uploads successfully and appears in the list.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Browser (both sessions).</t>
+          <t>Browser. The staff path was once client-only and every staff attach failed with 'Couldn't send'.</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -8129,27 +8141,27 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ATT-03</t>
+          <t>ATT-02</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Download via signed URL</t>
+          <t>Client upload</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Request a download URL, then fetch the blob.</t>
+          <t>Attach a file as a client user.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>The file downloads; the URL is time-limited and cannot be reused after expiry.</t>
+          <t>Uploads and is visible to staff.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>API + curl after the expiry window.</t>
+          <t>Browser (both sessions).</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -8169,37 +8181,49 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ATT-04</t>
+          <t>ATT-03</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Oversized file is refused</t>
+          <t>Download via signed URL</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Upload a file above the configured limit.</t>
+          <t>Request a download URL, then fetch the blob.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>The file downloads; the URL is time-limited and cannot be reused after expiry.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>API + curl after the expiry window.</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr"/>
-      <c r="I155" s="5" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>End to end on a local instance: the detail issued a five-minute signed URL (200), the blob route served the bytes (200) and the browser rendered the image in the thread. On PRODUCTION this path was returning Next's 404 page for every attachment until this run - the API mints links at the site origin, but nginx gives /api/* to the web app and the API publishes no port, so nothing reached it. A route was added; a bad signature now returns 401 from the API rather than 404 HTML from Next.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8209,27 +8233,27 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ATT-05</t>
+          <t>ATT-04</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Quarantined file cannot be downloaded</t>
+          <t>Oversized file is refused</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Upload the EICAR string, then attempt to download it.</t>
+          <t>Upload a file above the configured limit.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Blocked and badged as quarantined.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -8249,27 +8273,27 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ATT-06</t>
+          <t>ATT-05</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>PSA attachment sweep</t>
+          <t>Quarantined file cannot be downloaded</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Add an attachment in the PSA to a ticket nobody has touched, then sync.</t>
+          <t>Upload the EICAR string, then attempt to download it.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>It is imported by the dated sweep where the provider supports one (ConnectWise indexes documents per record and falls back to per-ticket).</t>
+          <t>Blocked and badged as quarantined.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Portal + worker log.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -8289,27 +8313,27 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ATT-07</t>
+          <t>ATT-06</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Deletion reconciliation</t>
+          <t>PSA attachment sweep</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Delete an attachment in the PSA and sync.</t>
+          <t>Add an attachment in the PSA to a ticket nobody has touched, then sync.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>It is removed from the portal.</t>
+          <t>It is imported by the dated sweep where the provider supports one (ConnectWise indexes documents per record and falls back to per-ticket).</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>SQL on attachments.</t>
+          <t>Portal + worker log.</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -8329,27 +8353,27 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ATT-08</t>
+          <t>ATT-07</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Multipart upload to Autotask</t>
+          <t>Deletion reconciliation</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Attach a file that must be pushed to Autotask.</t>
+          <t>Delete an attachment in the PSA and sync.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Sent as multipart, not JSON (the real API rejects JSON with 415).</t>
+          <t>It is removed from the portal.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Worker log + PSA UI.</t>
+          <t>SQL on attachments.</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -8364,32 +8388,32 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>15. Productivity and Analytics</t>
+          <t>14. Attachments</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ANA-01</t>
+          <t>ATT-08</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Technician metrics</t>
+          <t>Multipart upload to Autotask</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>GET /api/dashboard/technician for a technician with known ticket history.</t>
+          <t>Attach a file that must be pushed to Autotask.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Counts, SLA percentage, average resolution and logged time match SQL.</t>
+          <t>Sent as multipart, not JSON (the real API rejects JSON with 415).</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>API + SQL.</t>
+          <t>Worker log + PSA UI.</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -8409,27 +8433,27 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ANA-02</t>
+          <t>ANA-01</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Score renormalises over measured components</t>
+          <t>Technician metrics</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Inspect the productivity breakdown for a technician with no CSAT data.</t>
+          <t>GET /api/dashboard/technician for a technician with known ticket history.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Unmeasured components are EXCLUDED rather than scored as zero, and the coverage fraction is reported.</t>
+          <t>Counts, SLA percentage, average resolution and logged time match SQL.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>API response. A score computed over missing data is worse than no score.</t>
+          <t>API + SQL.</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -8449,27 +8473,27 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ANA-03</t>
+          <t>ANA-02</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer is always present</t>
+          <t>Score renormalises over measured components</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Call every dashboard endpoint.</t>
+          <t>Inspect the productivity breakdown for a technician with no CSAT data.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Each response carries the measurement disclaimer.</t>
+          <t>Unmeasured components are EXCLUDED rather than scored as zero, and the coverage fraction is reported.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Raw JSON.</t>
+          <t>API response. A score computed over missing data is worse than no score.</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -8489,27 +8513,27 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ANA-04</t>
+          <t>ANA-03</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Team view and export</t>
+          <t>Disclaimer is always present</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>GET /api/dashboard/team then /team/export.</t>
+          <t>Call every dashboard endpoint.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>The CSV matches the on-screen table exactly, including the header row.</t>
+          <t>Each response carries the measurement disclaimer.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Download and diff.</t>
+          <t>Raw JSON.</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -8529,27 +8553,27 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ANA-05</t>
+          <t>ANA-04</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Team view and export</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>GET /api/dashboard/trend over a range spanning a data gap.</t>
+          <t>GET /api/dashboard/team then /team/export.</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Gaps are visible as gaps, not interpolated to zero.</t>
+          <t>The CSV matches the on-screen table exactly, including the header row.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>API + chart.</t>
+          <t>Download and diff.</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -8569,27 +8593,27 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ANA-06</t>
+          <t>ANA-05</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Client workload ranking</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/analytics/clients.</t>
+          <t>GET /api/dashboard/trend over a range spanning a data gap.</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Clients ranked by hours; sample size shown; unclosable tickets excluded from averages.</t>
+          <t>Gaps are visible as gaps, not interpolated to zero.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>API + chart.</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -8609,27 +8633,27 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ANA-07</t>
+          <t>ANA-06</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>SLA percentage with no eligible tickets</t>
+          <t>Client workload ranking</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>View a client with zero SLA-eligible tickets.</t>
+          <t>Open /dashboard/analytics/clients.</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Shows null / not applicable - never 100 percent.</t>
+          <t>Clients ranked by hours; sample size shown; unclosable tickets excluded from averages.</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -8649,27 +8673,27 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>ANA-08</t>
+          <t>ANA-07</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Portal versus PSA coverage</t>
+          <t>SLA percentage with no eligible tickets</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/analytics/coverage.</t>
+          <t>View a client with zero SLA-eligible tickets.</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Coverage percentage plus ticket and day corroboration, and a flag when the range starts before activity recording began.</t>
+          <t>Shows null / not applicable - never 100 percent.</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Browser. Without that flag the early period looks like poor adoption rather than no data.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -8689,27 +8713,27 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ANA-09</t>
+          <t>ANA-08</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Own versus team scope</t>
+          <t>Portal versus PSA coverage</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>View analytics as a Technician (productivity.own.view) and as a Manager (productivity.team.view).</t>
+          <t>Open /dashboard/analytics/coverage.</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>The technician sees only themselves.</t>
+          <t>Coverage percentage plus ticket and day corroboration, and a flag when the range starts before activity recording began.</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser. Without that flag the early period looks like poor adoption rather than no data.</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -8729,27 +8753,27 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>ANA-10</t>
+          <t>ANA-09</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Analytics reflect the full ticket set</t>
+          <t>Own versus team scope</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Compare the ticket count behind analytics with the PSA's own count.</t>
+          <t>View analytics as a Technician (productivity.own.view) and as a Manager (productivity.team.view).</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>They match. Analytics computed over a truncated import were wrong for months before pagination was fixed.</t>
+          <t>The technician sees only themselves.</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>SQL vs PSA.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -8769,27 +8793,27 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ANA-11</t>
+          <t>ANA-10</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Ticket-derived metrics recompute on read</t>
+          <t>Analytics reflect the full ticket set</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Import more tickets, then reload analytics without any rollup running.</t>
+          <t>Compare the ticket count behind analytics with the PSA's own count.</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Client workload and technician metrics already reflect the new data.</t>
+          <t>They match. Analytics computed over a truncated import were wrong for months before pagination was fixed.</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>SQL vs PSA.</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -8809,27 +8833,27 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ANA-12</t>
+          <t>ANA-11</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Export respects permissions</t>
+          <t>Ticket-derived metrics recompute on read</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Request the team export as a Technician.</t>
+          <t>Import more tickets, then reload analytics without any rollup running.</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Refused.</t>
+          <t>Client workload and technician metrics already reflect the new data.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>API 403.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -8844,54 +8868,42 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>16. Activity Events and Daily Rollup</t>
+          <t>15. Productivity and Analytics</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ROLL-01</t>
+          <t>ANA-12</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Events are captured from both sources</t>
+          <t>Export respects permissions</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Perform a portal action and let a PSA transition sync.</t>
+          <t>Request the team export as a Technician.</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Rows appear in activity_events with Source Portal and Psa respectively.</t>
+          <t>Refused.</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "Source",count(*) from activity_events group by 1.</t>
+          <t>API 403.</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>Claude (agent), unattended - no interactive session available</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-05 / 06 / 07</t>
-        </is>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>Events captured from both sources.</t>
-        </is>
-      </c>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr"/>
+      <c r="I172" s="5" t="inlineStr"/>
+      <c r="J172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -8901,27 +8913,27 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>ROLL-02</t>
+          <t>ROLL-01</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Events are dated when they HAPPENED</t>
+          <t>Events are captured from both sources</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Import a ticket closed last month.</t>
+          <t>Perform a portal action and let a PSA transition sync.</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>OccurredAt carries last month's date, not today's.</t>
+          <t>Rows appear in activity_events with Source Portal and Psa respectively.</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>SQL: select "OccurredAt"::date, count(*) from activity_events group by 1 order by 1.</t>
+          <t>SQL: select "Source",count(*) from activity_events group by 1.</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -8941,7 +8953,7 @@
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>Events dated 13 Jul to 3 Sep - when they happened, not when they arrived.</t>
+          <t>Events captured from both sources.</t>
         </is>
       </c>
     </row>
@@ -8953,27 +8965,27 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>ROLL-03</t>
+          <t>ROLL-02</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Rollup produces daily facts</t>
+          <t>Events are dated when they HAPPENED</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Wait for the hourly pass or restart the worker.</t>
+          <t>Import a ticket closed last month.</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>activity_daily_facts is populated; sum("EventCount") equals the number of events in range.</t>
+          <t>OccurredAt carries last month's date, not today's.</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>SQL: select "OccurredAt"::date, count(*) from activity_events group by 1 order by 1.</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -8993,7 +9005,7 @@
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>68 events, 13 daily facts, all 68 aggregated.</t>
+          <t>Events dated 13 Jul to 3 Sep - when they happened, not when they arrived.</t>
         </is>
       </c>
     </row>
@@ -9005,22 +9017,22 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>ROLL-04</t>
+          <t>ROLL-03</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>History older than the rolling window is backfilled</t>
+          <t>Rollup produces daily facts</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Insert an event dated 60 days ago, then run the rollup.</t>
+          <t>Wait for the hourly pass or restart the worker.</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>A fact exists for that day. A fixed 7-day window alone can never build history.</t>
+          <t>activity_daily_facts is populated; sum("EventCount") equals the number of events in range.</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -9030,7 +9042,7 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -9045,7 +9057,7 @@
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>Needs a backdated event; injecting one would corrupt real analytics.</t>
+          <t>68 events, 13 daily facts, all 68 aggregated.</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9069,32 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>ROLL-05</t>
+          <t>ROLL-04</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Backfill settles</t>
+          <t>History older than the rolling window is backfilled</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Run the rollup twice.</t>
+          <t>Insert an event dated 60 days ago, then run the rollup.</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>The first pass processes the backlog; the second processes only the rolling window and the totals do not change.</t>
+          <t>A fact exists for that day. A fixed 7-day window alone can never build history.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Compare the two 'Activity rollup:' log lines - capture the first line's timestamp and poll for a DIFFERENT one, or you will read the same line twice.</t>
+          <t>SQL.</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -9097,7 +9109,7 @@
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>Three consecutive hourly passes identical - the backfill settled.</t>
+          <t>Needs a backdated event; injecting one would corrupt real analytics.</t>
         </is>
       </c>
     </row>
@@ -9109,32 +9121,32 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>ROLL-06</t>
+          <t>ROLL-05</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Late-arriving events correct their own day</t>
+          <t>Backfill settles</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Add a second event for a day already rolled up, then run the rollup.</t>
+          <t>Run the rollup twice.</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>That day's fact is rebuilt, not appended to.</t>
+          <t>The first pass processes the backlog; the second processes only the rolling window and the totals do not change.</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>Compare the two 'Activity rollup:' log lines - capture the first line's timestamp and poll for a DIFFERENT one, or you will read the same line twice.</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -9149,7 +9161,7 @@
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>As ROLL-04.</t>
+          <t>Three consecutive hourly passes identical - the backfill settled.</t>
         </is>
       </c>
     </row>
@@ -9161,22 +9173,22 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ROLL-07</t>
+          <t>ROLL-06</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Untouched days keep their facts</t>
+          <t>Late-arriving events correct their own day</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Ensure a day inside the rebuild range has facts but no new events.</t>
+          <t>Add a second event for a day already rolled up, then run the rollup.</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Its facts survive the pass unchanged.</t>
+          <t>That day's fact is rebuilt, not appended to.</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -9213,32 +9225,32 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>ROLL-08</t>
+          <t>ROLL-07</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Retention expires raw events but keeps facts</t>
+          <t>Untouched days keep their facts</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Insert an event older than 396 days and run the rollup.</t>
+          <t>Ensure a day inside the rebuild range has facts but no new events.</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>The raw event is deleted; facts from that period remain.</t>
+          <t>Its facts survive the pass unchanged.</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>SQL counts on both tables.</t>
+          <t>SQL.</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -9253,49 +9265,61 @@
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>Nothing is old enough to expire: the oldest event is 54 days against a 396-day horizon. Zero rows past the horizon is no violation, not proof that expiry works. The deletion path is unit-tested only.</t>
+          <t>As ROLL-04.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>17. Client Control Panel</t>
+          <t>16. Activity Events and Daily Rollup</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>CP-01</t>
+          <t>ROLL-08</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Capabilities drive the navigation</t>
+          <t>Retention expires raw events but keeps facts</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Open /control-panel as a client admin and as a delegated non-admin.</t>
+          <t>Insert an event older than 396 days and run the rollup.</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>The admin sees every section; the delegate sees only granted sections.</t>
+          <t>The raw event is deleted; facts from that period remain.</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Browser (two sessions).</t>
+          <t>SQL counts on both tables.</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
-      <c r="I180" s="5" t="inlineStr"/>
-      <c r="J180" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Nothing is old enough to expire: the oldest event is 54 days against a 396-day horizon. Zero rows past the horizon is no violation, not proof that expiry works. The deletion path is unit-tested only.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -9305,27 +9329,27 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>CP-02</t>
+          <t>CP-01</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Ticket instructions, global and per account</t>
+          <t>Capabilities drive the navigation</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Set global instructions, then an override for one account.</t>
+          <t>Open /control-panel as a client admin and as a delegated non-admin.</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>The account override wins for that account; others fall back to global.</t>
+          <t>The admin sees every section; the delegate sees only granted sections.</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket for each account and compare the amber panel.</t>
+          <t>Browser (two sessions).</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -9345,27 +9369,27 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>CP-03</t>
+          <t>CP-02</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Approvers CRUD</t>
+          <t>Ticket instructions, global and per account</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Add, edit and delete an approver.</t>
+          <t>Set global instructions, then an override for one account.</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Each operation persists and is audited.</t>
+          <t>The account override wins for that account; others fall back to global.</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL + audit log.</t>
+          <t>Open a ticket for each account and compare the amber panel.</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -9385,27 +9409,27 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>CP-04</t>
+          <t>CP-03</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Escalation levels</t>
+          <t>Approvers CRUD</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Create escalation levels and confirm ordering.</t>
+          <t>Add, edit and delete an approver.</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Levels persist in order.</t>
+          <t>Each operation persists and is audited.</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + SQL + audit log.</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -9425,27 +9449,27 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>CP-05</t>
+          <t>CP-04</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Business hours</t>
+          <t>Escalation levels</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Set a weekly schedule and save.</t>
+          <t>Create escalation levels and confirm ordering.</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Stored as a single row per account with the weekly schedule; reload shows the same values.</t>
+          <t>Levels persist in order.</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -9465,27 +9489,27 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>CP-06</t>
+          <t>CP-05</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Holidays, manual and imported</t>
+          <t>Business hours</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Add a holiday by hand, then import from the PSA (POST /api/control-panel/holidays/import-from-psa).</t>
+          <t>Set a weekly schedule and save.</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Imported holidays are de-duplicated BY DATE, so re-importing does not double them and a renamed holiday does not create a second row.</t>
+          <t>Stored as a single row per account with the weekly schedule; reload shows the same values.</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Run the import twice and compare counts.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -9505,27 +9529,27 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>CP-07</t>
+          <t>CP-06</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Accounts and devices</t>
+          <t>Holidays, manual and imported</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>View the account card and add a device.</t>
+          <t>Add a holiday by hand, then import from the PSA (POST /api/control-panel/holidays/import-from-psa).</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Persists and displays.</t>
+          <t>Imported holidays are de-duplicated BY DATE, so re-importing does not double them and a renamed holiday does not create a second row.</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Run the import twice and compare counts.</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -9545,27 +9569,27 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>CP-08</t>
+          <t>CP-07</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Announcements</t>
+          <t>Accounts and devices</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Create, pin, publish and unpublish an announcement.</t>
+          <t>View the account card and add a device.</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Only published announcements are visible to client users; pinned ones sort first.</t>
+          <t>Persists and displays.</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Browser (two sessions).</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -9585,27 +9609,27 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>CP-09</t>
+          <t>CP-08</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Knowledge base</t>
+          <t>Announcements</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Create a draft and a published FAQ article in two categories.</t>
+          <t>Create, pin, publish and unpublish an announcement.</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Drafts are hidden from client users; published ones are grouped by category.</t>
+          <t>Only published announcements are visible to client users; pinned ones sort first.</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser (two sessions).</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -9625,27 +9649,27 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>CP-10</t>
+          <t>CP-09</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Knowledge base</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Set display name, logo URL and accent colour.</t>
+          <t>Create a draft and a published FAQ article in two categories.</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>The live preview updates and the values persist.</t>
+          <t>Drafts are hidden from client users; published ones are grouped by category.</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Browser. Confirm a javascript: or data: URL in the logo field is REJECTED.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -9665,27 +9689,27 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>CP-11</t>
+          <t>CP-10</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Account report</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Open Control Panel &gt; Reports.</t>
+          <t>Set display name, logo URL and accent colour.</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Ticket counts by status, open count, hours logged and billable, and recent tickets - all matching SQL for that account.</t>
+          <t>The live preview updates and the values persist.</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>Browser. Confirm a javascript: or data: URL in the logo field is REJECTED.</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -9705,27 +9729,27 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>CP-12</t>
+          <t>CP-11</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Open-ticket count uses the mapped statuses</t>
+          <t>Account report</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Ensure a ticket carries an unmapped raw provider status, then view the report.</t>
+          <t>Open Control Panel &gt; Reports.</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>It is NOT counted as open, because the open list is NEW, IN_PROGRESS, WAITING_CUSTOMER, ON_HOLD. This is why unmapped statuses matter beyond cosmetics.</t>
+          <t>Ticket counts by status, open count, hours logged and billable, and recent tickets - all matching SQL for that account.</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL. Then map the status and confirm the count corrects itself.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -9745,27 +9769,27 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>CP-13</t>
+          <t>CP-12</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Delegation scope: one account versus all</t>
+          <t>Open-ticket count uses the mapped statuses</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Grant a user a section for one account, then for all accounts.</t>
+          <t>Ensure a ticket carries an unmapped raw provider status, then view the report.</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Access matches the scope exactly.</t>
+          <t>It is NOT counted as open, because the open list is NEW, IN_PROGRESS, WAITING_CUSTOMER, ON_HOLD. This is why unmapped statuses matter beyond cosmetics.</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + SQL. Then map the status and confirm the count corrects itself.</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -9785,27 +9809,27 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>CP-14</t>
+          <t>CP-13</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Control panel is client-only</t>
+          <t>Delegation scope: one account versus all</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Attempt /api/control-panel/* with a staff-only session.</t>
+          <t>Grant a user a section for one account, then for all accounts.</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Refused.</t>
+          <t>Access matches the scope exactly.</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>API.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -9820,32 +9844,32 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>18. Reports, Export and Scheduling</t>
+          <t>17. Client Control Panel</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>RPT-01</t>
+          <t>CP-14</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>CSV export is valid</t>
+          <t>Control panel is client-only</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>GET /api/control-panel/report/export.</t>
+          <t>Attempt /api/control-panel/* with a staff-only session.</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>RFC-4180 compliant: quoted fields, escaped quotes, correct header. Opens cleanly in Excel.</t>
+          <t>Refused.</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Download and open. Include a client name containing a comma and a quote.</t>
+          <t>API.</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -9865,27 +9889,27 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>RPT-02</t>
+          <t>RPT-01</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Create a schedule</t>
+          <t>CSV export is valid</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/control-panel/report/schedules with a frequency.</t>
+          <t>GET /api/control-panel/report/export.</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Stored with the correct next-run time.</t>
+          <t>RFC-4180 compliant: quoted fields, escaped quotes, correct header. Opens cleanly in Excel.</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>SQL on report_schedules.</t>
+          <t>Download and open. Include a client name containing a comma and a quote.</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -9905,27 +9929,27 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>RPT-03</t>
+          <t>RPT-02</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Run now</t>
+          <t>Create a schedule</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>POST /api/control-panel/report/schedules/{id}/run.</t>
+          <t>PUT /api/control-panel/report/schedules with a frequency.</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>A run is recorded and the file is downloadable.</t>
+          <t>Stored with the correct next-run time.</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL on report_runs.</t>
+          <t>SQL on report_schedules.</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -9945,27 +9969,27 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>RPT-04</t>
+          <t>RPT-03</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Scheduled runs fire</t>
+          <t>Run now</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Set a schedule due in the past and wait for the worker's 5-minute tick.</t>
+          <t>POST /api/control-panel/report/schedules/{id}/run.</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>The run executes once and the next-run time advances.</t>
+          <t>A run is recorded and the file is downloadable.</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>SQL + worker log. Confirm it does not run repeatedly.</t>
+          <t>Browser + SQL on report_runs.</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -9985,27 +10009,27 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>RPT-05</t>
+          <t>RPT-04</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Run history and download</t>
+          <t>Scheduled runs fire</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>GET /api/control-panel/report/runs then download one.</t>
+          <t>Set a schedule due in the past and wait for the worker's 5-minute tick.</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>History lists past runs; each downloads its own CSV.</t>
+          <t>The run executes once and the next-run time advances.</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>SQL + worker log. Confirm it does not run repeatedly.</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -10025,27 +10049,27 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>RPT-06</t>
+          <t>RPT-05</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>No email is sent</t>
+          <t>Run history and download</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Inspect the delivery path.</t>
+          <t>GET /api/control-panel/report/runs then download one.</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>There is no SMTP in the stack: reports and enquiries are STORED for in-portal download, never emailed. Verify expectations match this.</t>
+          <t>History lists past runs; each downloads its own CSV.</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Code/config review - this is a design fact worth confirming with the customer.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -10060,32 +10084,32 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>19. AI Assistant</t>
+          <t>18. Reports, Export and Scheduling</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>AI-01</t>
+          <t>RPT-06</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Disabled by default</t>
+          <t>No email is sent</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Open a ticket on a tenant that has never configured the assistant.</t>
+          <t>Inspect the delivery path.</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>No assistant actions are offered.</t>
+          <t>There is no SMTP in the stack: reports and enquiries are STORED for in-portal download, never emailed. Verify expectations match this.</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Code/config review - this is a design fact worth confirming with the customer.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -10105,27 +10129,27 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AI-01</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Enabling without a key is refused</t>
+          <t>Disabled by default</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Attempt to enable the assistant with no API key stored.</t>
+          <t>Open a ticket on a tenant that has never configured the assistant.</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>No assistant actions are offered.</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Browser + API.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -10145,27 +10169,27 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>The key is never returned</t>
+          <t>Enabling without a key is refused</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>GET /api/assistant/settings.</t>
+          <t>Attempt to enable the assistant with no API key stored.</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Returns hasKey true/false only - never the key itself.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Raw JSON.</t>
+          <t>Browser + API.</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -10185,27 +10209,27 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Internal notes are excluded by default</t>
+          <t>The key is never returned</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>With IncludeInternalNotes false, run Summarise on a ticket containing internal notes.</t>
+          <t>GET /api/assistant/settings.</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Internal content is not sent, and the prompt STATES the exclusion.</t>
+          <t>Returns hasKey true/false only - never the key itself.</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Inspect the outbound request in the API log/telemetry. This is a confidentiality control, not a preference.</t>
+          <t>Raw JSON.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -10225,27 +10249,27 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>AI-05</t>
+          <t>AI-04</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>All six actions work</t>
+          <t>Internal notes are excluded by default</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Run Summarise, DraftReply, ImproveDraft, NextSteps, ExplainError and SimilarTickets.</t>
+          <t>With IncludeInternalNotes false, run Summarise on a ticket containing internal notes.</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Each returns a useful result into the composer.</t>
+          <t>Internal content is not sent, and the prompt STATES the exclusion.</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Inspect the outbound request in the API log/telemetry. This is a confidentiality control, not a preference.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -10265,27 +10289,27 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AI-05</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>The assistant writes nothing</t>
+          <t>All six actions work</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Run every action and then inspect the ticket.</t>
+          <t>Run Summarise, DraftReply, ImproveDraft, NextSteps, ExplainError and SimilarTickets.</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>No note, status change or time entry is created - drafts land in the composer only.</t>
+          <t>Each returns a useful result into the composer.</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>SQL before/after.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -10305,27 +10329,27 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>AI-07</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Provider errors are translated</t>
+          <t>The assistant writes nothing</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Configure a deliberately invalid key and run an action.</t>
+          <t>Run every action and then inspect the ticket.</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>401/403 becomes 'check the key', 429 becomes 'wait', and 400 shows the provider's own message.</t>
+          <t>No note, status change or time entry is created - drafts land in the composer only.</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>SQL before/after.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -10345,27 +10369,27 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>AI-08</t>
+          <t>AI-07</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Ticket scope is checked before the model is called</t>
+          <t>Provider errors are translated</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Request an assistant action for a ticket the user may not see.</t>
+          <t>Configure a deliberately invalid key and run an action.</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Refused BEFORE any call to the provider.</t>
+          <t>401/403 becomes 'check the key', 429 becomes 'wait', and 400 shows the provider's own message.</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>API + absence of an outbound request in the log.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -10380,32 +10404,32 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>20. Notifications, Audit and Background Jobs</t>
+          <t>19. AI Assistant</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>AI-08</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Notification list and history</t>
+          <t>Ticket scope is checked before the model is called</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>GET /api/me/notifications and /notifications/history.</t>
+          <t>Request an assistant action for a ticket the user may not see.</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Own-data sections are visible to every authenticated user regardless of role.</t>
+          <t>Refused BEFORE any call to the provider.</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Browser as a Technician.</t>
+          <t>API + absence of an outbound request in the log.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -10425,27 +10449,27 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Audit trail is written</t>
+          <t>Notification list and history</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Perform a connection edit, a role change and a mapping change.</t>
+          <t>GET /api/me/notifications and /notifications/history.</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Each appears in /dashboard/audit with actor, action and target.</t>
+          <t>Own-data sections are visible to every authenticated user regardless of role.</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL on audit_logs.</t>
+          <t>Browser as a Technician.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -10465,27 +10489,27 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Audit records no secrets</t>
+          <t>Audit trail is written</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Rotate a credential and inspect the audit entry.</t>
+          <t>Perform a connection edit, a role change and a mapping change.</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>The entry records that a rotation happened, with no credential value.</t>
+          <t>Each appears in /dashboard/audit with actor, action and target.</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>SQL on the audit payload.</t>
+          <t>Browser + SQL on audit_logs.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -10505,27 +10529,27 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Audit is append-only</t>
+          <t>Audit records no secrets</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Attempt to modify or delete an audit row through the application.</t>
+          <t>Rotate a credential and inspect the audit entry.</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>No such path exists.</t>
+          <t>The entry records that a rotation happened, with no credential value.</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>API surface review.</t>
+          <t>SQL on the audit payload.</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -10545,27 +10569,27 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Job list and dead-letter queue</t>
+          <t>Audit is append-only</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Open /dashboard/jobs.</t>
+          <t>Attempt to modify or delete an audit row through the application.</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Queued, running, failed and DLQ jobs are listed with their attempt counts.</t>
+          <t>No such path exists.</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>API surface review.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -10585,27 +10609,27 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>OPS-05</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Reprocess a dead-lettered job</t>
+          <t>Job list and dead-letter queue</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/jobs/{id}/reprocess on a DLQ job, then on a non-DLQ job.</t>
+          <t>Open /dashboard/jobs.</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>The DLQ job is re-queued and audited; the non-DLQ one is refused.</t>
+          <t>Queued, running, failed and DLQ jobs are listed with their attempt counts.</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>API + SQL.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -10625,27 +10649,27 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>OPS-07</t>
+          <t>OPS-06</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Retry and backoff</t>
+          <t>Reprocess a dead-lettered job</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Force a transient failure in a job handler.</t>
+          <t>POST /api/admin/jobs/{id}/reprocess on a DLQ job, then on a non-DLQ job.</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>It retries with backoff and lands in the DLQ only after the configured attempts.</t>
+          <t>The DLQ job is re-queued and audited; the non-DLQ one is refused.</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>Worker log + SQL.</t>
+          <t>API + SQL.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -10665,27 +10689,27 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>OPS-08</t>
+          <t>OPS-07</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Storage usage</t>
+          <t>Retry and backoff</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>GET /api/admin/storage.</t>
+          <t>Force a transient failure in a job handler.</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Reported usage matches actual attachment storage.</t>
+          <t>It retries with backoff and lands in the DLQ only after the configured attempts.</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>API + storage inspection.</t>
+          <t>Worker log + SQL.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -10700,54 +10724,42 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>21. Public Site, Enquiries and Legal</t>
+          <t>20. Notifications, Audit and Background Jobs</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>PUB-01</t>
+          <t>OPS-08</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Marketing pages render</t>
+          <t>Storage usage</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Visit /, /about, /faq, /contact, /book, /platform, /security, /integrations and every /features/{slug}.</t>
+          <t>GET /api/admin/storage.</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>All render with no console errors and no broken links.</t>
+          <t>Reported usage matches actual attachment storage.</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>Browser DevTools.</t>
+          <t>API + storage inspection.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr">
-        <is>
-          <t>Claude (agent), unattended - no interactive session available</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-05 / 06 / 07</t>
-        </is>
-      </c>
-      <c r="J216" s="4" t="inlineStr">
-        <is>
-          <t>All 17 public pages return 200 with real content, not a shell.</t>
-        </is>
-      </c>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr"/>
+      <c r="I216" s="5" t="inlineStr"/>
+      <c r="J216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -10757,27 +10769,27 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>PUB-02</t>
+          <t>PUB-01</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Contact enquiry is stored</t>
+          <t>Marketing pages render</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Submit the contact form.</t>
+          <t>Visit /, /about, /faq, /contact, /book, /platform, /security, /integrations and every /features/{slug}.</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>A row appears in enquiries and in /dashboard/enquiries. Nothing is emailed - by design.</t>
+          <t>All render with no console errors and no broken links.</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Browser + SQL.</t>
+          <t>Browser DevTools.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -10797,7 +10809,7 @@
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>Stored with Kind = 0. The test rows were deleted afterwards; the one genuine enquiry on production was left alone.</t>
+          <t>All 17 public pages return 200 with real content, not a shell.</t>
         </is>
       </c>
     </row>
@@ -10809,27 +10821,27 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>PUB-03</t>
+          <t>PUB-02</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Meeting request</t>
+          <t>Contact enquiry is stored</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Submit the booking form.</t>
+          <t>Submit the contact form.</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Stored and visible to staff with enquiries.view.</t>
+          <t>A row appears in enquiries and in /dashboard/enquiries. Nothing is emailed - by design.</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Browser + SQL.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -10849,7 +10861,7 @@
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>Stored with Kind = 1, carrying the preferred time as the visitor worded it.</t>
+          <t>Stored with Kind = 0. The test rows were deleted afterwards; the one genuine enquiry on production was left alone.</t>
         </is>
       </c>
     </row>
@@ -10861,27 +10873,27 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>PUB-04</t>
+          <t>PUB-03</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Honeypot silently absorbs bots</t>
+          <t>Meeting request</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>POST /api/public/enquiries/contact with the 'website' field filled.</t>
+          <t>Submit the booking form.</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Returns 202 and stores NOTHING.</t>
+          <t>Stored and visible to staff with enquiries.view.</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>curl + SQL count unchanged.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -10901,7 +10913,7 @@
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>A filled honeypot answers 202 and stores nothing - confirmed by row count.</t>
+          <t>Stored with Kind = 1, carrying the preferred time as the visitor worded it.</t>
         </is>
       </c>
     </row>
@@ -10913,27 +10925,27 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>PUB-05</t>
+          <t>PUB-04</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Enquiry validation</t>
+          <t>Honeypot silently absorbs bots</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Submit with a missing required field and with an oversized payload.</t>
+          <t>POST /api/public/enquiries/contact with the 'website' field filled.</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Rejected with a validation error, never a 500.</t>
+          <t>Returns 202 and stores NOTHING.</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>curl. A required attribute on a positional record parameter has twice caused a 500 on every request - this is the guard test.</t>
+          <t>curl + SQL count unchanged.</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -10953,7 +10965,7 @@
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t>A defect this run, now fixed and verified in production. A 60,000-character message used to return 202 and store exactly 4,000: the sender was thanked and never told, and staff read a message ending mid-sentence with nothing to mark the cut. Every visitor-typed field is now refused when oversized, naming the field and the limit, and nothing is written on a refusal. Live: 60,000 and 4,001 both 400, a normal message 202, no truncated rows. SourcePage is still clipped on purpose - the site fills it in, and a lead should not be lost to the length of our own URL.</t>
+          <t>A filled honeypot answers 202 and stores nothing - confirmed by row count.</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10977,32 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>PUB-06</t>
+          <t>PUB-05</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Enquiry status workflow</t>
+          <t>Enquiry validation</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/enquiries/{id}/status.</t>
+          <t>Submit with a missing required field and with an oversized payload.</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Status updates and is audited.</t>
+          <t>Rejected with a validation error, never a 500.</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>curl. A required attribute on a positional record parameter has twice caused a 500 on every request - this is the guard test.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -11005,7 +11017,7 @@
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>Needs an admin session to move an enquiry through its statuses.</t>
+          <t>A defect this run, now fixed and verified in production. A 60,000-character message used to return 202 and store exactly 4,000: the sender was thanked and never told, and staff read a message ending mid-sentence with nothing to mark the cut. Every visitor-typed field is now refused when oversized, naming the field and the limit, and nothing is written on a refusal. Live: 60,000 and 4,001 both 400, a normal message 202, no truncated rows. SourcePage is still clipped on purpose - the site fills it in, and a lead should not be lost to the length of our own URL.</t>
         </is>
       </c>
     </row>
@@ -11017,32 +11029,32 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>PUB-07</t>
+          <t>PUB-06</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Legal pages complete</t>
+          <t>Enquiry status workflow</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Open /privacy and /terms.</t>
+          <t>POST /api/admin/enquiries/{id}/status.</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Both render with working anchors. CHECK for unfilled placeholder slots - registered address, hosting region, retention periods, liability cap and governing law were left deliberately blank for the owner to supply.</t>
+          <t>Status updates and is audited.</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Browser. Shipping these with placeholders visible to customers is a real risk.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -11057,7 +11069,7 @@
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>Twelve unfilled placeholders are live and visible: seven on /privacy (registered address, hosting provider, hosting region, and four retention periods reading "e.g. 24 months" and the like) and five on /terms (two notice periods, the liability cap "e.g. the fees paid in the preceding 12 months", and governing law twice as "your jurisdiction"). A scan for placeholder MARKERS - TBD, TODO, lorem ipsum - finds nothing, because the slots hold ordinary English inside &lt;mark&gt; elements; only grepping "&lt;Fill" in the page sources revealed them. Needs the owner's real values.</t>
+          <t>Needs an admin session to move an enquiry through its statuses.</t>
         </is>
       </c>
     </row>
@@ -11069,32 +11081,32 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>PUB-08</t>
+          <t>PUB-07</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>No cookie banner is needed</t>
+          <t>Legal pages complete</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Inspect cookies on the public site.</t>
+          <t>Open /privacy and /terms.</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Session cookies only, no analytics - which is why no consent banner is present. Confirm this is still true before adding any third-party script.</t>
+          <t>Both render with working anchors. CHECK for unfilled placeholder slots - registered address, hosting region, retention periods, liability cap and governing law were left deliberately blank for the owner to supply.</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>DevTools &gt; Application &gt; Cookies.</t>
+          <t>Browser. Shipping these with placeholders visible to customers is a real risk.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -11109,39 +11121,39 @@
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>Zero cookies are set on any public page, so no banner is owed. The session cookies begin at sign-in and are strictly necessary.</t>
+          <t>Twelve unfilled placeholders are live and visible: seven on /privacy (registered address, hosting provider, hosting region, and four retention periods reading "e.g. 24 months" and the like) and five on /terms (two notice periods, the liability cap "e.g. the fees paid in the preceding 12 months", and governing law twice as "your jurisdiction"). A scan for placeholder MARKERS - TBD, TODO, lorem ipsum - finds nothing, because the slots hold ordinary English inside &lt;mark&gt; elements; only grepping "&lt;Fill" in the page sources revealed them. Needs the owner's real values.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>22. Performance, Scale and Resilience</t>
+          <t>21. Public Site, Enquiries and Legal</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>PERF-01</t>
+          <t>PUB-08</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Full re-sync duration is known</t>
+          <t>No cookie banner is needed</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Time a full re-sync: set LastSuccessfulSyncAt to null and watch until the timestamp returns.</t>
+          <t>Inspect cookies on the public site.</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Record the duration against the ticket count. It scales roughly linearly because each ticket triggers note import, assignee resolution and a time refresh.</t>
+          <t>Session cookies only, no analytics - which is why no consent banner is present. Confirm this is still true before adding any third-party script.</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>SQL timestamps. At 135 tickets this is 15-20 minutes; plan accordingly at 1,000+.</t>
+          <t>DevTools &gt; Application &gt; Cookies.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -11161,7 +11173,7 @@
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>A full re-sync of 135 tickets takes about 8 minutes and 279 requests, after two efficiencies landed this run.</t>
+          <t>Zero cookies are set on any public page, so no banner is owed. The session cookies begin at sign-in and are strictly necessary.</t>
         </is>
       </c>
     </row>
@@ -11173,27 +11185,27 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>PERF-02</t>
+          <t>PERF-01</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Incremental sync stays cheap</t>
+          <t>Full re-sync duration is known</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Observe a quiet 5-minute cycle.</t>
+          <t>Time a full re-sync: set LastSuccessfulSyncAt to null and watch until the timestamp returns.</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Only changed tickets are processed; a no-op cycle logs nothing and simply advances the timestamp.</t>
+          <t>Record the duration against the ticket count. It scales roughly linearly because each ticket triggers note import, assignee resolution and a time refresh.</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Worker log + SQL.</t>
+          <t>SQL timestamps. At 135 tickets this is 15-20 minutes; plan accordingly at 1,000+.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -11213,7 +11225,7 @@
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
-          <t>A quiet cycle costs about three outbound requests.</t>
+          <t>A full re-sync of 135 tickets takes about 8 minutes and 279 requests, after two efficiencies landed this run.</t>
         </is>
       </c>
     </row>
@@ -11225,27 +11237,27 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>PERF-03</t>
+          <t>PERF-02</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Page cap headroom</t>
+          <t>Incremental sync stays cheap</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Compare the ticket count in range with 50 pages x 100 per page.</t>
+          <t>Observe a quiet 5-minute cycle.</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Comfortably under 5,000. Beyond that the cap truncates - and now warns.</t>
+          <t>Only changed tickets are processed; a no-op cycle logs nothing and simply advances the timestamp.</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>SQL + log.</t>
+          <t>Worker log + SQL.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -11265,7 +11277,7 @@
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>2.7% and 0.3% of the 5,000-ticket ceiling.</t>
+          <t>A quiet cycle costs about three outbound requests.</t>
         </is>
       </c>
     </row>
@@ -11277,32 +11289,32 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>PERF-04</t>
+          <t>PERF-03</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Ticket list performance</t>
+          <t>Page cap headroom</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Load the ticket list for the largest client.</t>
+          <t>Compare the ticket count in range with 50 pages x 100 per page.</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Loads within an acceptable time; the supporting indexes are in place.</t>
+          <t>Comfortably under 5,000. Beyond that the cap truncates - and now warns.</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Browser timing + EXPLAIN on the query.</t>
+          <t>SQL + log.</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -11317,7 +11329,7 @@
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>Needs a session.</t>
+          <t>2.7% and 0.3% of the 5,000-ticket ceiling.</t>
         </is>
       </c>
     </row>
@@ -11329,27 +11341,27 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>PERF-05</t>
+          <t>PERF-04</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Concurrent users</t>
+          <t>Ticket list performance</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Have several testers use the portal simultaneously during a sync.</t>
+          <t>Load the ticket list for the largest client.</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>No deadlocks or timeouts; the rollup's batched deletes do not block dashboard reads.</t>
+          <t>Loads within an acceptable time; the supporting indexes are in place.</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Observation + database locks.</t>
+          <t>Browser timing + EXPLAIN on the query.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -11369,7 +11381,7 @@
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>Needs several concurrent testers.</t>
+          <t>Needs a session.</t>
         </is>
       </c>
     </row>
@@ -11381,27 +11393,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>PERF-06</t>
+          <t>PERF-05</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Recovery after an outage</t>
+          <t>Concurrent users</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Stop the PSA connection (or the database) briefly, then restore it.</t>
+          <t>Have several testers use the portal simultaneously during a sync.</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>The worker resumes on the next cycle without manual intervention, and a failed pass repairs itself rather than leaving a permanent hole.</t>
+          <t>No deadlocks or timeouts; the rollup's batched deletes do not block dashboard reads.</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Worker log.</t>
+          <t>Observation + database locks.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -11421,44 +11433,44 @@
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>Would mean deliberately breaking production.</t>
+          <t>Needs several concurrent testers.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>23. Regression Traps - Defects Already Found in This Build</t>
+          <t>22. Performance, Scale and Resilience</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>REG-01</t>
+          <t>PERF-06</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Sync imports EVERY ticket, not the first page</t>
+          <t>Recovery after an outage</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Full re-sync with more tickets than the page size.</t>
+          <t>Stop the PSA connection (or the database) briefly, then restore it.</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Count matches the PSA. Regression symptom: exactly 100 (or N x 100) tickets.</t>
+          <t>The worker resumes on the next cycle without manual intervention, and a failed pass repairs itself rather than leaving a permanent hole.</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>SQL vs PSA count.</t>
+          <t>Worker log.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -11473,7 +11485,7 @@
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>135 imported with no duplicates.</t>
+          <t>Would mean deliberately breaking production.</t>
         </is>
       </c>
     </row>
@@ -11485,27 +11497,27 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>REG-02</t>
+          <t>REG-01</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Every written field is in the update hash</t>
+          <t>Sync imports EVERY ticket, not the first page</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Change one field at a time in the PSA and sync.</t>
+          <t>Full re-sync with more tickets than the page size.</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Each change lands. Regression symptom: a field that never updates on existing rows while new tickets look correct.</t>
+          <t>Count matches the PSA. Regression symptom: exactly 100 (or N x 100) tickets.</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>SQL per field. Has occurred for the raise date and for the queue.</t>
+          <t>SQL vs PSA count.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -11525,7 +11537,7 @@
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>Dates and queue all populated; both gaps were found and closed this run.</t>
+          <t>135 imported with no duplicates.</t>
         </is>
       </c>
     </row>
@@ -11537,27 +11549,27 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>REG-03</t>
+          <t>REG-02</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Mapping actually maps</t>
+          <t>Every written field is in the update hash</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>After any connector change, check PsaStatus versus PortalStatus.</t>
+          <t>Change one field at a time in the PSA and sync.</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>They differ wherever a rule exists. Regression symptom: PsaStatus = PortalStatus on every row, which looks exactly like a deliberate pass-through.</t>
+          <t>Each change lands. Regression symptom: a field that never updates on existing rows while new tickets look correct.</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>SQL per field. Has occurred for the raise date and for the queue.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -11577,7 +11589,7 @@
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>Zero raw statuses or priorities on either connection.</t>
+          <t>Dates and queue all populated; both gaps were found and closed this run.</t>
         </is>
       </c>
     </row>
@@ -11589,27 +11601,27 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>REG-04</t>
+          <t>REG-03</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Discovery offers what tickets arrive with</t>
+          <t>Mapping actually maps</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Save a mapping through the UI, then sync.</t>
+          <t>After any connector change, check PsaStatus versus PortalStatus.</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>The saved rule matches incoming tickets. Regression symptom: rules hold ids while tickets carry names.</t>
+          <t>They differ wherever a rule exists. Regression symptom: PsaStatus = PortalStatus on every row, which looks exactly like a deliberate pass-through.</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>SQL + the certification tests.</t>
+          <t>SQL.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -11629,7 +11641,7 @@
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>Discovery now offers the value tickets arrive with, held by certification tests on both providers.</t>
+          <t>Zero raw statuses or priorities on either connection.</t>
         </is>
       </c>
     </row>
@@ -11641,27 +11653,27 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>REG-05</t>
+          <t>REG-04</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Autotask next page is POSTed</t>
+          <t>Discovery offers what tickets arrive with</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Full Autotask re-sync spanning more than one page.</t>
+          <t>Save a mapping through the UI, then sync.</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>No 405 'does not support http method GET'.</t>
+          <t>The saved rule matches incoming tickets. Regression symptom: rules hold ids while tickets carry names.</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>Worker log.</t>
+          <t>SQL + the certification tests.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -11681,7 +11693,7 @@
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>No 405 on the Autotask next page; the fake now refuses a GET as the live API does.</t>
+          <t>Discovery now offers the value tickets arrive with, held by certification tests on both providers.</t>
         </is>
       </c>
     </row>
@@ -11693,32 +11705,32 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>REG-06</t>
+          <t>REG-05</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Note title does not duplicate the body</t>
+          <t>Autotask next page is POSTed</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Post a long note to Autotask.</t>
+          <t>Full Autotask re-sync spanning more than one page.</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Rendered once.</t>
+          <t>No 405 'does not support http method GET'.</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Autotask UI.</t>
+          <t>Worker log.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -11733,7 +11745,7 @@
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>Needs a portal-side note.</t>
+          <t>No 405 on the Autotask next page; the fake now refuses a GET as the live API does.</t>
         </is>
       </c>
     </row>
@@ -11745,27 +11757,27 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>REG-07</t>
+          <t>REG-06</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Internal notes are not dropped</t>
+          <t>Note title does not duplicate the body</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Autotask time entry with internal-only text.</t>
+          <t>Post a long note to Autotask.</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Text preserved.</t>
+          <t>Rendered once.</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Portal thread.</t>
+          <t>Autotask UI.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -11785,7 +11797,7 @@
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>Needs a PSA time entry with internal-only text.</t>
+          <t>Needs a portal-side note.</t>
         </is>
       </c>
     </row>
@@ -11797,27 +11809,27 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>REG-08</t>
+          <t>REG-07</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Retired picklist values are filtered</t>
+          <t>Internal notes are not dropped</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Retire a value in the PSA and refresh fields.</t>
+          <t>Autotask time entry with internal-only text.</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Not offered; existing rules flagged.</t>
+          <t>Text preserved.</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>Browser.</t>
+          <t>Portal thread.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -11837,7 +11849,7 @@
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>Needs a picklist value retired in the PSA.</t>
+          <t>Needs a PSA time entry with internal-only text.</t>
         </is>
       </c>
     </row>
@@ -11849,32 +11861,32 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>REG-09</t>
+          <t>REG-08</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Rollup builds history, not just the last week</t>
+          <t>Retired picklist values are filtered</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Insert an event older than seven days and run the rollup.</t>
+          <t>Retire a value in the PSA and refresh fields.</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>A fact is created for it.</t>
+          <t>Not offered; existing rules flagged.</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>SQL.</t>
+          <t>Browser.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -11889,7 +11901,7 @@
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>Facts cover July to September, not just the rolling window.</t>
+          <t>Needs a picklist value retired in the PSA.</t>
         </is>
       </c>
     </row>
@@ -11901,53 +11913,105 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
+          <t>REG-09</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Rollup builds history, not just the last week</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Insert an event older than seven days and run the rollup.</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>A fact is created for it.</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>SQL.</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>Facts cover July to September, not just the rolling window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>23. Regression Traps - Defects Already Found in This Build</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
           <t>REG-10</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>Fakes must not be more permissive than the real API</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>When adding connector behaviour, make the in-memory fake enforce what the provider enforces.</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>The unit suite fails before production does. Every connector bug in this list was hidden at least once by a fake that accepted something the real API rejects.</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>dotnet test tests/unit.</t>
         </is>
       </c>
-      <c r="G239" s="4" t="inlineStr">
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H239" s="4" t="inlineStr">
-        <is>
-          <t>Claude (agent), unattended - no interactive session available</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-05 / 06 / 07</t>
-        </is>
-      </c>
-      <c r="J239" s="4" t="inlineStr">
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>Claude (agent), unattended - no interactive session available</t>
+        </is>
+      </c>
+      <c r="I240" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-05 / 06 / 07</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
         <is>
           <t>549 unit tests green; five defects this run were each hidden at least once by a fake more permissive than the real API, and each fake was tightened.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J239"/>
-  <conditionalFormatting sqref="G2:G239">
+  <autoFilter ref="A1:J240"/>
+  <conditionalFormatting sqref="G2:G240">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11962,7 +12026,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G239" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Result" prompt="Pick a result" type="list">
+    <dataValidation sqref="G2:G240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Result" prompt="Pick a result" type="list">
       <formula1>"Not run,Pass,Partial,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12046,23 +12110,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A5)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A5,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A5,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A5,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A5,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A5,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A5,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A5,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A5,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G5" s="12">
@@ -12077,23 +12141,23 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A6)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A6,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A6,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A6,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A6,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A6,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A6,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A6,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A6,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G6" s="15">
@@ -12108,23 +12172,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A7)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A7,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A7,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A7,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A7,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A7,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A7,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A7,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A7,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G7" s="12">
@@ -12139,23 +12203,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A8)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A8,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A8,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A8,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A8,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A8,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A8,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A8,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A8,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G8" s="15">
@@ -12170,23 +12234,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A9)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A9,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A9,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A9,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A9,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A9,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A9,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A9,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A9,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G9" s="12">
@@ -12201,23 +12265,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A10)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A10,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A10,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A10,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A10,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A10,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A10,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A10,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A10,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G10" s="15">
@@ -12232,23 +12296,23 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A11)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A11,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A11,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A11,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A11,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E11" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A11,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A11,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F11" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A11,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A11,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G11" s="12">
@@ -12263,23 +12327,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A12)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A12,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A12,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A12,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A12,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A12,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A12,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A12,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A12,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G12" s="15">
@@ -12294,23 +12358,23 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A13)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A13,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A13,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A13,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A13,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A13,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A13,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F13" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A13,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A13,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G13" s="12">
@@ -12325,23 +12389,23 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A14)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A14,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A14,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A14,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A14,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A14,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A14,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A14,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A14,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G14" s="15">
@@ -12356,23 +12420,23 @@
         </is>
       </c>
       <c r="B15" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A15)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A15,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A15,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A15,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A15,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A15,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A15,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F15" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A15,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A15,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G15" s="12">
@@ -12387,23 +12451,23 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A16)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A16,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A16,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A16,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A16,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A16,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A16,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A16,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A16,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G16" s="15">
@@ -12418,23 +12482,23 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A17)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A17,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A17,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A17,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A17,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A17,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A17,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A17,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A17,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G17" s="12">
@@ -12449,23 +12513,23 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A18)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A18,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A18,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A18,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A18,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A18,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A18,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A18,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A18,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G18" s="15">
@@ -12480,23 +12544,23 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A19)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A19,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A19,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A19,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A19,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A19,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A19,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A19,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A19,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G19" s="12">
@@ -12511,23 +12575,23 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A20)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A20,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A20,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A20,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A20,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A20,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A20,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A20,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A20,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G20" s="15">
@@ -12542,23 +12606,23 @@
         </is>
       </c>
       <c r="B21" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A21)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A21,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A21,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A21,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A21,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A21,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A21,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A21,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A21,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G21" s="12">
@@ -12573,23 +12637,23 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A22)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A22,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A22,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A22,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A22,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A22,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A22,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A22,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A22,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G22" s="15">
@@ -12604,23 +12668,23 @@
         </is>
       </c>
       <c r="B23" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A23)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A23,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A23,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A23,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A23,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E23" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A23,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A23,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F23" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A23,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A23,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G23" s="12">
@@ -12635,23 +12699,23 @@
         </is>
       </c>
       <c r="B24" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A24)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A24,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A24,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D24" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A24,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A24,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E24" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A24,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A24,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F24" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A24,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A24,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G24" s="15">
@@ -12666,23 +12730,23 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A25)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A25,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A25,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A25,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A25,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E25" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A25,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A25,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F25" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A25,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A25,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G25" s="12">
@@ -12697,23 +12761,23 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A26)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A26,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A26,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D26" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A26,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A26,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E26" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A26,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A26,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F26" s="14">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A26,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A26,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G26" s="15">
@@ -12728,23 +12792,23 @@
         </is>
       </c>
       <c r="B27" s="11">
-        <f>COUNTIF('Test Cases'!$A$2:$A$239,$A27)</f>
+        <f>COUNTIF('Test Cases'!$A$2:$A$240,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A27,'Test Cases'!$G$2:$G$239,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A27,'Test Cases'!$G$2:$G$240,"Pass")</f>
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A27,'Test Cases'!$G$2:$G$239,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A27,'Test Cases'!$G$2:$G$240,"Fail")</f>
         <v/>
       </c>
       <c r="E27" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A27,'Test Cases'!$G$2:$G$239,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A27,'Test Cases'!$G$2:$G$240,"Blocked")</f>
         <v/>
       </c>
       <c r="F27" s="11">
-        <f>COUNTIFS('Test Cases'!$A$2:$A$239,$A27,'Test Cases'!$G$2:$G$239,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$A$2:$A$240,$A27,'Test Cases'!$G$2:$G$240,"Not run")</f>
         <v/>
       </c>
       <c r="G27" s="12">

--- a/docs/qa/desk-portal-test-cases.xlsx
+++ b/docs/qa/desk-portal-test-cases.xlsx
@@ -11106,7 +11106,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>Twelve unfilled placeholders are live and visible: seven on /privacy (registered address, hosting provider, hosting region, and four retention periods reading "e.g. 24 months" and the like) and five on /terms (two notice periods, the liability cap "e.g. the fees paid in the preceding 12 months", and governing law twice as "your jurisdiction"). A scan for placeholder MARKERS - TBD, TODO, lorem ipsum - finds nothing, because the slots hold ordinary English inside &lt;mark&gt; elements; only grepping "&lt;Fill" in the page sources revealed them. Needs the owner's real values.</t>
+          <t>Failed when first run: twelve unfilled placeholders were live and visible - seven on /privacy and five on /terms, including retention periods reading "e.g. 24 months" and governing law as "your jurisdiction". A scan for placeholder MARKERS (TBD, TODO, lorem ipsum) found nothing, because the slots held ordinary English inside &lt;mark&gt; elements; only grepping "&lt;Fill" in the page sources revealed them. All twelve are now filled and zero &lt;mark&gt; spans remain on either live page. The retention ones were not blanks but promises: nothing deletes enquiries or audit records and logs rotate at 14 days, so the policy states what the system actually does rather than periods no code enforces. Hosting is named from the host's own network (Hostinger, United States) - the owner should confirm the region in their panel, as it decides whether EU data is being transferred.</t>
         </is>
       </c>
     </row>
